--- a/output/売上表_平日土日別.xlsx
+++ b/output/売上表_平日土日別.xlsx
@@ -9,8 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="月別集計" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="平日" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="土日" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="グラフ" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="平日" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="土日" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="日別推移データ" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="49">
   <si>
     <r>
       <rPr>
@@ -795,6 +797,378 @@
   </si>
   <si>
     <t xml:space="preserve">・青字の売上は入力値。修正すると全集計に反映されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平日・土日 売上グラフ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青＝平日　オレンジ＝土日（※祝日は平日に含む）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→ 全期間平均：平日 約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円／土日 約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">61</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円。土日は平日の約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月以降はどちらも下降傾向。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日〜、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日まで。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は報告なしの日があるため実際より少なめ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※空白部分は報告のない期間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">日付</t>
@@ -892,20 +1266,29 @@
       <t xml:space="preserve">）</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">平日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土日</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0\日"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.00\倍"/>
-    <numFmt numFmtId="169" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="169" formatCode="#,##0,\千"/>
+    <numFmt numFmtId="170" formatCode="#,##0,,&quot;百万&quot;"/>
+    <numFmt numFmtId="171" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="172" formatCode="m/d"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -994,6 +1377,39 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -1016,20 +1432,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
-        <bgColor rgb="FF595959"/>
+        <fgColor rgb="FF2A78D6"/>
+        <bgColor rgb="FF0066CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC55A11"/>
-        <bgColor rgb="FF993300"/>
+        <fgColor rgb="FFEB6834"/>
+        <bgColor rgb="FFFF8080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE3E2DE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1082,7 +1498,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1151,11 +1567,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1163,7 +1587,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1181,6 +1605,26 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1209,7 +1653,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFE7E6E6"/>
@@ -1217,7 +1661,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1228,18 +1672,18 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE3E2DE"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFC55A11"/>
+      <rgbColor rgb="FFEB6834"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -1248,11 +1692,2068 @@
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2F5597"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>① 1日あたり平均売上（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"平日 1日平均"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 1日平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0,\千" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>月別集計!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>月別集計!$D$4:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>380992.857142857</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>421276.842105263</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>336752.727272727</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>279522.272727273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>230350.909090909</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"土日 1日平均"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 1日平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0,\千" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>月別集計!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>月別集計!$G$4:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>686633.333333333</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>726590</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>602112.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>537923.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>484307.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="-8"/>
+        <c:axId val="86558956"/>
+        <c:axId val="28011317"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="86558956"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="28011317"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="28011317"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="86558956"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>② 月別売上合計（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"平日"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="ffffff"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0,\千" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>月別集計!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>月別集計!$C$4:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2666950</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8004260</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3704280</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6149490</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2533860</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"土日"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="ffffff"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0,\千" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>月別集計!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>月別集計!$F$4:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2059900</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5812720</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2408450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4303390</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1937230</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
+        <c:axId val="8612957"/>
+        <c:axId val="4836804"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="8612957"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="4836804"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="4836804"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,,&quot;百万&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="8612957"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>③ 日別売上の推移（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>日別推移データ!B1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>日別推移データ!$A$2:$A$98</c:f>
+              <c:strCache>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>6/21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6/23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6/24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6/25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6/26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6/27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6/28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6/29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6/30</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7/1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7/2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7/3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7/4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7/5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7/6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7/7</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7/8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7/9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7/10</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7/11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7/12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7/13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7/14</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7/15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7/16</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7/17</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7/18</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7/19</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7/20</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7/25</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7/26</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7/27</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7/28</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7/29</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7/30</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7/31</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8/1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8/2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8/3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8/4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8/5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8/6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8/7</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8/24</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8/25</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8/26</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8/27</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8/28</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8/29</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8/30</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8/31</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9/1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9/2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9/3</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9/4</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9/5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9/6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9/7</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9/8</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9/9</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>9/10</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>9/11</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>9/12</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9/13</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>9/14</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9/15</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9/16</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>9/17</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>9/18</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>9/19</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>9/20</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>9/21</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>9/22</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>9/23</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>9/24</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9/25</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9/26</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>9/27</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>9/28</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>9/29</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>9/30</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>10/1</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>10/2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10/3</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>10/4</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10/5</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>10/6</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>10/7</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>10/8</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>10/9</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>10/10</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>10/11</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>10/12</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>10/13</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>10/14</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>10/15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>日別推移データ!$B$2:$B$98</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="1">
+                  <c:v>386840</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>377840</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>428620</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>374210</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>459300</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>335720</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>304420</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>454040</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>421760</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>526640</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>294280</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>332760</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>375800</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>425290</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>474820</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>372650</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>289840</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>418780</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>459900</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>493180</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>597070</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>395610</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>357540</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>383270</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>397380</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>533650</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>363910</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>360990</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>383160</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>388830</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>449020</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>268730</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>256280</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>351140</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>299580</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>362970</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>219670</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>228460</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>214940</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>263030</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>212930</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>207730</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>335170</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>212760</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>294500</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>320850</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>215510</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>167060</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>392050</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>259100</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>278990</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>606440</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>471650</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>425490</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>223490</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>235170</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>175910</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>203590</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>204670</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>165390</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>250680</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>190960</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>237070</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>264350</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>211130</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>247550</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>344250</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>167680</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>241620</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>213180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>日別推移データ!C1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>日別推移データ!$A$2:$A$98</c:f>
+              <c:strCache>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>6/21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6/23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6/24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6/25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6/26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6/27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6/28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6/29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6/30</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7/1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7/2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7/3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7/4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7/5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7/6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7/7</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7/8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7/9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7/10</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7/11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7/12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7/13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7/14</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7/15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7/16</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7/17</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7/18</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7/19</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7/20</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7/25</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7/26</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7/27</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7/28</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7/29</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7/30</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7/31</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8/1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8/2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8/3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8/4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8/5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8/6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8/7</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8/24</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8/25</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8/26</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8/27</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8/28</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8/29</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8/30</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8/31</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9/1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9/2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9/3</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9/4</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9/5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9/6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9/7</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9/8</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9/9</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>9/10</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>9/11</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>9/12</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9/13</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>9/14</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9/15</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9/16</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>9/17</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>9/18</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>9/19</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>9/20</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>9/21</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>9/22</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>9/23</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>9/24</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9/25</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9/26</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>9/27</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>9/28</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>9/29</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>9/30</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>10/1</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>10/2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10/3</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>10/4</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10/5</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>10/6</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>10/7</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>10/8</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>10/9</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>10/10</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>10/11</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>10/12</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>10/13</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>10/14</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>10/15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>日別推移データ!$C$2:$C$98</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>636370</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>716170</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>707360</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>833600</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>717490</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>773400</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>786550</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>652640</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>737850</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>615300</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>695890</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>664790</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>711580</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>554810</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>477270</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>573870</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>543590</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>507490</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>543290</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>466800</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>586850</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>569450</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>512050</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>454190</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>606680</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>377970</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>498390</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="30"/>
+        <c:overlap val="100"/>
+        <c:axId val="21385023"/>
+        <c:axId val="13427211"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="21385023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="13427211"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="13427211"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,\千" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="21385023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>364680</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>162000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="571680"/>
+        <a:ext cx="6479640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>364680</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>172800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="4191120"/>
+        <a:ext cx="6479640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>171360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>403920</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>162360</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="7810560"/>
+        <a:ext cx="10799640" cy="3599640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1765,6 +4266,51 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:A63"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1777,1221 +4323,1221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="20" t="n">
         <v>46195</v>
       </c>
-      <c r="B2" s="19" t="str">
+      <c r="B2" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A2),1)</f>
         <v>月</v>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="22" t="n">
         <v>386840</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>30</v>
+      <c r="D2" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>46196</v>
       </c>
-      <c r="B3" s="19" t="str">
+      <c r="B3" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A3),1)</f>
         <v>火</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="22" t="n">
         <v>377840</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>30</v>
+      <c r="D3" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="20" t="n">
         <v>46197</v>
       </c>
-      <c r="B4" s="19" t="str">
+      <c r="B4" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A4),1)</f>
         <v>水</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="22" t="n">
         <v>428620</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>30</v>
+      <c r="D4" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="20" t="n">
         <v>46198</v>
       </c>
-      <c r="B5" s="19" t="str">
+      <c r="B5" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A5),1)</f>
         <v>木</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="22" t="n">
         <v>374210</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>31</v>
+      <c r="D5" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="20" t="n">
         <v>46199</v>
       </c>
-      <c r="B6" s="19" t="str">
+      <c r="B6" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A6),1)</f>
         <v>金</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="22" t="n">
         <v>459300</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>31</v>
+      <c r="D6" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="20" t="n">
         <v>46202</v>
       </c>
-      <c r="B7" s="19" t="str">
+      <c r="B7" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A7),1)</f>
         <v>月</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="22" t="n">
         <v>335720</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>31</v>
+      <c r="D7" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="20" t="n">
         <v>46203</v>
       </c>
-      <c r="B8" s="19" t="str">
+      <c r="B8" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A8),1)</f>
         <v>火</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="22" t="n">
         <v>304420</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>32</v>
+      <c r="D8" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="20" t="n">
         <v>46204</v>
       </c>
-      <c r="B9" s="19" t="str">
+      <c r="B9" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A9),1)</f>
         <v>水</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>454040</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>30</v>
+      <c r="D9" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="20" t="n">
         <v>46205</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A10),1)</f>
         <v>木</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>421760</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>32</v>
+      <c r="D10" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="20" t="n">
         <v>46206</v>
       </c>
-      <c r="B11" s="19" t="str">
+      <c r="B11" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A11),1)</f>
         <v>金</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="22" t="n">
         <v>526640</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>31</v>
+      <c r="D11" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="20" t="n">
         <v>46209</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B12" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A12),1)</f>
         <v>月</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="22" t="n">
         <v>294280</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>30</v>
+      <c r="D12" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="20" t="n">
         <v>46210</v>
       </c>
-      <c r="B13" s="19" t="str">
+      <c r="B13" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A13),1)</f>
         <v>火</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="22" t="n">
         <v>332760</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>30</v>
+      <c r="D13" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="20" t="n">
         <v>46211</v>
       </c>
-      <c r="B14" s="19" t="str">
+      <c r="B14" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A14),1)</f>
         <v>水</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="22" t="n">
         <v>375800</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>32</v>
+      <c r="D14" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="20" t="n">
         <v>46212</v>
       </c>
-      <c r="B15" s="19" t="str">
+      <c r="B15" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A15),1)</f>
         <v>木</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="22" t="n">
         <v>425290</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>31</v>
+      <c r="D15" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="20" t="n">
         <v>46213</v>
       </c>
-      <c r="B16" s="19" t="str">
+      <c r="B16" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A16),1)</f>
         <v>金</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="22" t="n">
         <v>474820</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>30</v>
+      <c r="D16" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="20" t="n">
         <v>46216</v>
       </c>
-      <c r="B17" s="19" t="str">
+      <c r="B17" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A17),1)</f>
         <v>月</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="22" t="n">
         <v>372650</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>32</v>
+      <c r="D17" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="20" t="n">
         <v>46217</v>
       </c>
-      <c r="B18" s="19" t="str">
+      <c r="B18" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A18),1)</f>
         <v>火</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="22" t="n">
         <v>289840</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>30</v>
+      <c r="D18" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="20" t="n">
         <v>46218</v>
       </c>
-      <c r="B19" s="19" t="str">
+      <c r="B19" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A19),1)</f>
         <v>水</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="22" t="n">
         <v>418780</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>32</v>
+      <c r="D19" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="20" t="n">
         <v>46219</v>
       </c>
-      <c r="B20" s="19" t="str">
+      <c r="B20" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A20),1)</f>
         <v>木</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="22" t="n">
         <v>459900</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>32</v>
+      <c r="D20" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="20" t="n">
         <v>46220</v>
       </c>
-      <c r="B21" s="19" t="str">
+      <c r="B21" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A21),1)</f>
         <v>金</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="22" t="n">
         <v>493180</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>32</v>
+      <c r="D21" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="20" t="n">
         <v>46223</v>
       </c>
-      <c r="B22" s="19" t="str">
+      <c r="B22" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A22),1)</f>
         <v>月</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="22" t="n">
         <v>597070</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>33</v>
+      <c r="D22" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>38</v>
       </c>
       <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="20" t="n">
         <v>46230</v>
       </c>
-      <c r="B23" s="19" t="str">
+      <c r="B23" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A23),1)</f>
         <v>月</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="22" t="n">
         <v>395610</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>31</v>
+      <c r="D23" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="20" t="n">
         <v>46231</v>
       </c>
-      <c r="B24" s="19" t="str">
+      <c r="B24" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A24),1)</f>
         <v>火</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="22" t="n">
         <v>357540</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>34</v>
+      <c r="D24" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="20" t="n">
         <v>46232</v>
       </c>
-      <c r="B25" s="19" t="str">
+      <c r="B25" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A25),1)</f>
         <v>水</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="22" t="n">
         <v>383270</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>31</v>
+      <c r="D25" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="20" t="n">
         <v>46233</v>
       </c>
-      <c r="B26" s="19" t="str">
+      <c r="B26" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A26),1)</f>
         <v>木</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="22" t="n">
         <v>397380</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>32</v>
+      <c r="D26" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="20" t="n">
         <v>46234</v>
       </c>
-      <c r="B27" s="19" t="str">
+      <c r="B27" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A27),1)</f>
         <v>金</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="22" t="n">
         <v>533650</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>34</v>
+      <c r="D27" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="20" t="n">
         <v>46237</v>
       </c>
-      <c r="B28" s="19" t="str">
+      <c r="B28" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A28),1)</f>
         <v>月</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="22" t="n">
         <v>363910</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>32</v>
+      <c r="D28" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="20" t="n">
         <v>46238</v>
       </c>
-      <c r="B29" s="19" t="str">
+      <c r="B29" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A29),1)</f>
         <v>火</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="22" t="n">
         <v>360990</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>34</v>
+      <c r="D29" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="20" t="n">
         <v>46239</v>
       </c>
-      <c r="B30" s="19" t="str">
+      <c r="B30" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A30),1)</f>
         <v>水</v>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="22" t="n">
         <v>383160</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>34</v>
+      <c r="D30" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="20" t="n">
         <v>46240</v>
       </c>
-      <c r="B31" s="19" t="str">
+      <c r="B31" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A31),1)</f>
         <v>木</v>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="22" t="n">
         <v>388830</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>32</v>
+      <c r="D31" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="20" t="n">
         <v>46241</v>
       </c>
-      <c r="B32" s="19" t="str">
+      <c r="B32" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A32),1)</f>
         <v>金</v>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="22" t="n">
         <v>449020</v>
       </c>
-      <c r="D32" s="21" t="s">
-        <v>32</v>
+      <c r="D32" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="20" t="n">
         <v>46258</v>
       </c>
-      <c r="B33" s="19" t="str">
+      <c r="B33" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A33),1)</f>
         <v>月</v>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="22" t="n">
         <v>268730</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>32</v>
+      <c r="D33" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="20" t="n">
         <v>46259</v>
       </c>
-      <c r="B34" s="19" t="str">
+      <c r="B34" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A34),1)</f>
         <v>火</v>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="22" t="n">
         <v>256280</v>
       </c>
-      <c r="D34" s="21" t="s">
-        <v>32</v>
+      <c r="D34" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="20" t="n">
         <v>46260</v>
       </c>
-      <c r="B35" s="19" t="str">
+      <c r="B35" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A35),1)</f>
         <v>水</v>
       </c>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="22" t="n">
         <v>351140</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>34</v>
+      <c r="D35" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="20" t="n">
         <v>46261</v>
       </c>
-      <c r="B36" s="19" t="str">
+      <c r="B36" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A36),1)</f>
         <v>木</v>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="22" t="n">
         <v>299580</v>
       </c>
-      <c r="D36" s="21" t="s">
-        <v>30</v>
+      <c r="D36" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="20" t="n">
         <v>46262</v>
       </c>
-      <c r="B37" s="19" t="str">
+      <c r="B37" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A37),1)</f>
         <v>金</v>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="22" t="n">
         <v>362970</v>
       </c>
-      <c r="D37" s="21" t="s">
-        <v>34</v>
+      <c r="D37" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="20" t="n">
         <v>46265</v>
       </c>
-      <c r="B38" s="19" t="str">
+      <c r="B38" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A38),1)</f>
         <v>月</v>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="22" t="n">
         <v>219670</v>
       </c>
-      <c r="D38" s="21" t="s">
-        <v>34</v>
+      <c r="D38" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="20" t="n">
         <v>46266</v>
       </c>
-      <c r="B39" s="19" t="str">
+      <c r="B39" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A39),1)</f>
         <v>火</v>
       </c>
-      <c r="C39" s="20" t="n">
+      <c r="C39" s="22" t="n">
         <v>228460</v>
       </c>
-      <c r="D39" s="21" t="s">
-        <v>34</v>
+      <c r="D39" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="20" t="n">
         <v>46267</v>
       </c>
-      <c r="B40" s="19" t="str">
+      <c r="B40" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A40),1)</f>
         <v>水</v>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="22" t="n">
         <v>214940</v>
       </c>
-      <c r="D40" s="21" t="s">
-        <v>30</v>
+      <c r="D40" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="20" t="n">
         <v>46268</v>
       </c>
-      <c r="B41" s="19" t="str">
+      <c r="B41" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A41),1)</f>
         <v>木</v>
       </c>
-      <c r="C41" s="20" t="n">
+      <c r="C41" s="22" t="n">
         <v>263030</v>
       </c>
-      <c r="D41" s="21" t="s">
-        <v>34</v>
+      <c r="D41" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="20" t="n">
         <v>46269</v>
       </c>
-      <c r="B42" s="19" t="str">
+      <c r="B42" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A42),1)</f>
         <v>金</v>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="22" t="n">
         <v>212930</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>34</v>
+      <c r="D42" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="20" t="n">
         <v>46272</v>
       </c>
-      <c r="B43" s="19" t="str">
+      <c r="B43" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A43),1)</f>
         <v>月</v>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C43" s="22" t="n">
         <v>207730</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>32</v>
+      <c r="D43" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="20" t="n">
         <v>46273</v>
       </c>
-      <c r="B44" s="19" t="str">
+      <c r="B44" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A44),1)</f>
         <v>火</v>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="22" t="n">
         <v>335170</v>
       </c>
-      <c r="D44" s="21" t="s">
-        <v>32</v>
+      <c r="D44" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="20" t="n">
         <v>46274</v>
       </c>
-      <c r="B45" s="19" t="str">
+      <c r="B45" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A45),1)</f>
         <v>水</v>
       </c>
-      <c r="C45" s="20" t="n">
+      <c r="C45" s="22" t="n">
         <v>212760</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>34</v>
+      <c r="D45" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="20" t="n">
         <v>46275</v>
       </c>
-      <c r="B46" s="19" t="str">
+      <c r="B46" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A46),1)</f>
         <v>木</v>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="22" t="n">
         <v>294500</v>
       </c>
-      <c r="D46" s="21" t="s">
-        <v>34</v>
+      <c r="D46" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="20" t="n">
         <v>46276</v>
       </c>
-      <c r="B47" s="19" t="str">
+      <c r="B47" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A47),1)</f>
         <v>金</v>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C47" s="22" t="n">
         <v>320850</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>32</v>
+      <c r="D47" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="20" t="n">
         <v>46279</v>
       </c>
-      <c r="B48" s="19" t="str">
+      <c r="B48" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A48),1)</f>
         <v>月</v>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C48" s="22" t="n">
         <v>215510</v>
       </c>
-      <c r="D48" s="21" t="s">
-        <v>34</v>
+      <c r="D48" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="20" t="n">
         <v>46280</v>
       </c>
-      <c r="B49" s="19" t="str">
+      <c r="B49" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A49),1)</f>
         <v>火</v>
       </c>
-      <c r="C49" s="20" t="n">
+      <c r="C49" s="22" t="n">
         <v>167060</v>
       </c>
-      <c r="D49" s="21" t="s">
-        <v>30</v>
+      <c r="D49" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="20" t="n">
         <v>46281</v>
       </c>
-      <c r="B50" s="19" t="str">
+      <c r="B50" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A50),1)</f>
         <v>水</v>
       </c>
-      <c r="C50" s="20" t="n">
+      <c r="C50" s="22" t="n">
         <v>392050</v>
       </c>
-      <c r="D50" s="21" t="s">
-        <v>34</v>
+      <c r="D50" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="20" t="n">
         <v>46282</v>
       </c>
-      <c r="B51" s="19" t="str">
+      <c r="B51" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A51),1)</f>
         <v>木</v>
       </c>
-      <c r="C51" s="20" t="n">
+      <c r="C51" s="22" t="n">
         <v>259100</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>32</v>
+      <c r="D51" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="20" t="n">
         <v>46283</v>
       </c>
-      <c r="B52" s="19" t="str">
+      <c r="B52" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A52),1)</f>
         <v>金</v>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C52" s="22" t="n">
         <v>278990</v>
       </c>
-      <c r="D52" s="21" t="s">
-        <v>32</v>
+      <c r="D52" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="20" t="n">
         <v>46286</v>
       </c>
-      <c r="B53" s="19" t="str">
+      <c r="B53" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A53),1)</f>
         <v>月</v>
       </c>
-      <c r="C53" s="20" t="n">
+      <c r="C53" s="22" t="n">
         <v>606440</v>
       </c>
-      <c r="D53" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>35</v>
+      <c r="D53" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="F53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="20" t="n">
         <v>46287</v>
       </c>
-      <c r="B54" s="19" t="str">
+      <c r="B54" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A54),1)</f>
         <v>火</v>
       </c>
-      <c r="C54" s="20" t="n">
+      <c r="C54" s="22" t="n">
         <v>471650</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="21" t="s">
+      <c r="D54" s="23" t="s">
         <v>36</v>
       </c>
+      <c r="E54" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="F54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="20" t="n">
         <v>46288</v>
       </c>
-      <c r="B55" s="19" t="str">
+      <c r="B55" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A55),1)</f>
         <v>水</v>
       </c>
-      <c r="C55" s="20" t="n">
+      <c r="C55" s="22" t="n">
         <v>425490</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>37</v>
+      <c r="D55" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="F55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="20" t="n">
         <v>46289</v>
       </c>
-      <c r="B56" s="19" t="str">
+      <c r="B56" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A56),1)</f>
         <v>木</v>
       </c>
-      <c r="C56" s="20" t="n">
+      <c r="C56" s="22" t="n">
         <v>223490</v>
       </c>
-      <c r="D56" s="21" t="s">
-        <v>32</v>
+      <c r="D56" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="20" t="n">
         <v>46290</v>
       </c>
-      <c r="B57" s="19" t="str">
+      <c r="B57" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A57),1)</f>
         <v>金</v>
       </c>
-      <c r="C57" s="20" t="n">
+      <c r="C57" s="22" t="n">
         <v>235170</v>
       </c>
-      <c r="D57" s="21" t="s">
-        <v>32</v>
+      <c r="D57" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="20" t="n">
         <v>46293</v>
       </c>
-      <c r="B58" s="19" t="str">
+      <c r="B58" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A58),1)</f>
         <v>月</v>
       </c>
-      <c r="C58" s="20" t="n">
+      <c r="C58" s="22" t="n">
         <v>175910</v>
       </c>
-      <c r="D58" s="21" t="s">
-        <v>32</v>
+      <c r="D58" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="20" t="n">
         <v>46294</v>
       </c>
-      <c r="B59" s="19" t="str">
+      <c r="B59" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A59),1)</f>
         <v>火</v>
       </c>
-      <c r="C59" s="20" t="n">
+      <c r="C59" s="22" t="n">
         <v>203590</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>34</v>
+      <c r="D59" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="20" t="n">
         <v>46295</v>
       </c>
-      <c r="B60" s="19" t="str">
+      <c r="B60" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A60),1)</f>
         <v>水</v>
       </c>
-      <c r="C60" s="20" t="n">
+      <c r="C60" s="22" t="n">
         <v>204670</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>34</v>
+      <c r="D60" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="20" t="n">
         <v>46296</v>
       </c>
-      <c r="B61" s="19" t="str">
+      <c r="B61" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A61),1)</f>
         <v>木</v>
       </c>
-      <c r="C61" s="20" t="n">
+      <c r="C61" s="22" t="n">
         <v>165390</v>
       </c>
-      <c r="D61" s="21" t="s">
-        <v>32</v>
+      <c r="D61" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="20" t="n">
         <v>46297</v>
       </c>
-      <c r="B62" s="19" t="str">
+      <c r="B62" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A62),1)</f>
         <v>金</v>
       </c>
-      <c r="C62" s="20" t="n">
+      <c r="C62" s="22" t="n">
         <v>250680</v>
       </c>
-      <c r="D62" s="21" t="s">
-        <v>34</v>
+      <c r="D62" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="20" t="n">
         <v>46300</v>
       </c>
-      <c r="B63" s="19" t="str">
+      <c r="B63" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A63),1)</f>
         <v>月</v>
       </c>
-      <c r="C63" s="20" t="n">
+      <c r="C63" s="22" t="n">
         <v>190960</v>
       </c>
-      <c r="D63" s="21" t="s">
-        <v>34</v>
+      <c r="D63" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="20" t="n">
         <v>46301</v>
       </c>
-      <c r="B64" s="19" t="str">
+      <c r="B64" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A64),1)</f>
         <v>火</v>
       </c>
-      <c r="C64" s="20" t="n">
+      <c r="C64" s="22" t="n">
         <v>237070</v>
       </c>
-      <c r="D64" s="21" t="s">
-        <v>34</v>
+      <c r="D64" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="20" t="n">
         <v>46302</v>
       </c>
-      <c r="B65" s="19" t="str">
+      <c r="B65" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A65),1)</f>
         <v>水</v>
       </c>
-      <c r="C65" s="20" t="n">
+      <c r="C65" s="22" t="n">
         <v>264350</v>
       </c>
-      <c r="D65" s="21" t="s">
-        <v>32</v>
+      <c r="D65" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="20" t="n">
         <v>46303</v>
       </c>
-      <c r="B66" s="19" t="str">
+      <c r="B66" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A66),1)</f>
         <v>木</v>
       </c>
-      <c r="C66" s="20" t="n">
+      <c r="C66" s="22" t="n">
         <v>211130</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>34</v>
+      <c r="D66" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="18" t="n">
+      <c r="A67" s="20" t="n">
         <v>46304</v>
       </c>
-      <c r="B67" s="19" t="str">
+      <c r="B67" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A67),1)</f>
         <v>金</v>
       </c>
-      <c r="C67" s="20" t="n">
+      <c r="C67" s="22" t="n">
         <v>247550</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>34</v>
+      <c r="D67" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="18" t="n">
+      <c r="A68" s="20" t="n">
         <v>46307</v>
       </c>
-      <c r="B68" s="19" t="str">
+      <c r="B68" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A68),1)</f>
         <v>月</v>
       </c>
-      <c r="C68" s="20" t="n">
+      <c r="C68" s="22" t="n">
         <v>344250</v>
       </c>
-      <c r="D68" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>38</v>
+      <c r="D68" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>43</v>
       </c>
       <c r="F68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="18" t="n">
+      <c r="A69" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B69" s="19" t="str">
+      <c r="B69" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A69),1)</f>
         <v>火</v>
       </c>
-      <c r="C69" s="20" t="n">
+      <c r="C69" s="22" t="n">
         <v>167680</v>
       </c>
-      <c r="D69" s="21" t="s">
-        <v>34</v>
+      <c r="D69" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="18" t="n">
+      <c r="A70" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B70" s="19" t="str">
+      <c r="B70" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A70),1)</f>
         <v>水</v>
       </c>
-      <c r="C70" s="20" t="n">
+      <c r="C70" s="22" t="n">
         <v>241620</v>
       </c>
-      <c r="D70" s="21" t="s">
-        <v>34</v>
+      <c r="D70" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="18" t="n">
+      <c r="A71" s="20" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="19" t="str">
+      <c r="B71" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A71),1)</f>
         <v>木</v>
       </c>
-      <c r="C71" s="20" t="n">
+      <c r="C71" s="22" t="n">
         <v>213180</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>32</v>
+      <c r="D71" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
@@ -3000,14 +5546,14 @@
       <c r="A72" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="22" t="n">
+      <c r="C72" s="24" t="n">
         <f aca="false">SUM(C2:C71)</f>
         <v>23058840</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C73" s="15" t="n">
         <f aca="false">COUNT(C2:C71)</f>
@@ -3015,10 +5561,10 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C74" s="22" t="n">
+      <c r="A74" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="24" t="n">
         <f aca="false">IF(C73=0,0,C72/C73)</f>
         <v>329412</v>
       </c>
@@ -3034,7 +5580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3051,482 +5597,482 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="20" t="n">
         <v>46194</v>
       </c>
-      <c r="B2" s="19" t="str">
+      <c r="B2" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A2),1)</f>
         <v>日</v>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="22" t="n">
         <v>636370</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>31</v>
+      <c r="D2" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>46200</v>
       </c>
-      <c r="B3" s="19" t="str">
+      <c r="B3" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A3),1)</f>
         <v>土</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="22" t="n">
         <v>716170</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>30</v>
+      <c r="D3" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="20" t="n">
         <v>46201</v>
       </c>
-      <c r="B4" s="19" t="str">
+      <c r="B4" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A4),1)</f>
         <v>日</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="22" t="n">
         <v>707360</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>31</v>
+      <c r="D4" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="20" t="n">
         <v>46207</v>
       </c>
-      <c r="B5" s="19" t="str">
+      <c r="B5" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A5),1)</f>
         <v>土</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="22" t="n">
         <v>833600</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>31</v>
+      <c r="D5" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="20" t="n">
         <v>46208</v>
       </c>
-      <c r="B6" s="19" t="str">
+      <c r="B6" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A6),1)</f>
         <v>日</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="22" t="n">
         <v>717490</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>30</v>
+      <c r="D6" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="20" t="n">
         <v>46214</v>
       </c>
-      <c r="B7" s="19" t="str">
+      <c r="B7" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A7),1)</f>
         <v>土</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="22" t="n">
         <v>773400</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>30</v>
+      <c r="D7" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="20" t="n">
         <v>46215</v>
       </c>
-      <c r="B8" s="19" t="str">
+      <c r="B8" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A8),1)</f>
         <v>日</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="22" t="n">
         <v>786550</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>30</v>
+      <c r="D8" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="20" t="n">
         <v>46221</v>
       </c>
-      <c r="B9" s="19" t="str">
+      <c r="B9" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A9),1)</f>
         <v>土</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>652640</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>31</v>
+      <c r="D9" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="20" t="n">
         <v>46222</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A10),1)</f>
         <v>日</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>737850</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>32</v>
+      <c r="D10" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="20" t="n">
         <v>46228</v>
       </c>
-      <c r="B11" s="19" t="str">
+      <c r="B11" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A11),1)</f>
         <v>土</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="22" t="n">
         <v>615300</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>32</v>
+      <c r="D11" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="20" t="n">
         <v>46229</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B12" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A12),1)</f>
         <v>日</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="22" t="n">
         <v>695890</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>34</v>
+      <c r="D12" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="21" t="s">
-        <v>41</v>
+      <c r="F12" s="23" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="20" t="n">
         <v>46235</v>
       </c>
-      <c r="B13" s="19" t="str">
+      <c r="B13" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A13),1)</f>
         <v>土</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="22" t="n">
         <v>664790</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>34</v>
+      <c r="D13" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="20" t="n">
         <v>46236</v>
       </c>
-      <c r="B14" s="19" t="str">
+      <c r="B14" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A14),1)</f>
         <v>日</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="22" t="n">
         <v>711580</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>34</v>
+      <c r="D14" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="20" t="n">
         <v>46263</v>
       </c>
-      <c r="B15" s="19" t="str">
+      <c r="B15" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A15),1)</f>
         <v>土</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="22" t="n">
         <v>554810</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>34</v>
+      <c r="D15" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="20" t="n">
         <v>46264</v>
       </c>
-      <c r="B16" s="19" t="str">
+      <c r="B16" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A16),1)</f>
         <v>日</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="22" t="n">
         <v>477270</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>31</v>
+      <c r="D16" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="20" t="n">
         <v>46270</v>
       </c>
-      <c r="B17" s="19" t="str">
+      <c r="B17" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A17),1)</f>
         <v>土</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="22" t="n">
         <v>573870</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>31</v>
+      <c r="D17" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="20" t="n">
         <v>46271</v>
       </c>
-      <c r="B18" s="19" t="str">
+      <c r="B18" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A18),1)</f>
         <v>日</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="22" t="n">
         <v>543590</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>34</v>
+      <c r="D18" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="20" t="n">
         <v>46277</v>
       </c>
-      <c r="B19" s="19" t="str">
+      <c r="B19" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A19),1)</f>
         <v>土</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="22" t="n">
         <v>507490</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>34</v>
+      <c r="D19" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="20" t="n">
         <v>46278</v>
       </c>
-      <c r="B20" s="19" t="str">
+      <c r="B20" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A20),1)</f>
         <v>日</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="22" t="n">
         <v>543290</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>34</v>
+      <c r="D20" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="20" t="n">
         <v>46284</v>
       </c>
-      <c r="B21" s="19" t="str">
+      <c r="B21" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A21),1)</f>
         <v>土</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="22" t="n">
         <v>466800</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>34</v>
+      <c r="D21" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="20" t="n">
         <v>46285</v>
       </c>
-      <c r="B22" s="19" t="str">
+      <c r="B22" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A22),1)</f>
         <v>日</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="22" t="n">
         <v>586850</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>34</v>
+      <c r="D22" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="20" t="n">
         <v>46291</v>
       </c>
-      <c r="B23" s="19" t="str">
+      <c r="B23" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A23),1)</f>
         <v>土</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="22" t="n">
         <v>569450</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>31</v>
+      <c r="D23" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="20" t="n">
         <v>46292</v>
       </c>
-      <c r="B24" s="19" t="str">
+      <c r="B24" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A24),1)</f>
         <v>日</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="22" t="n">
         <v>512050</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>34</v>
+      <c r="D24" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="20" t="n">
         <v>46298</v>
       </c>
-      <c r="B25" s="19" t="str">
+      <c r="B25" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A25),1)</f>
         <v>土</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="22" t="n">
         <v>454190</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>34</v>
+      <c r="D25" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="20" t="n">
         <v>46299</v>
       </c>
-      <c r="B26" s="19" t="str">
+      <c r="B26" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A26),1)</f>
         <v>日</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="22" t="n">
         <v>606680</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>34</v>
+      <c r="D26" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="20" t="n">
         <v>46305</v>
       </c>
-      <c r="B27" s="19" t="str">
+      <c r="B27" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A27),1)</f>
         <v>土</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="22" t="n">
         <v>377970</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>34</v>
+      <c r="D27" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="20" t="n">
         <v>46306</v>
       </c>
-      <c r="B28" s="19" t="str">
+      <c r="B28" s="21" t="str">
         <f aca="false">MID("日月火水木金土",WEEKDAY(A28),1)</f>
         <v>日</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="22" t="n">
         <v>498390</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>34</v>
+      <c r="D28" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -3535,14 +6081,14 @@
       <c r="A29" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="24" t="n">
         <f aca="false">SUM(C2:C28)</f>
         <v>16521690</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">COUNT(C2:C28)</f>
@@ -3550,12 +6096,1307 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="22" t="n">
+      <c r="A31" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="24" t="n">
         <f aca="false">IF(C30=0,0,C29/C30)</f>
         <v>611914.444444445</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C98"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="30" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A2,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C2" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A2,土日!$A$2:$A$28,0)),"")</f>
+        <v>636370</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B3" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A3,平日!$A$2:$A$71,0)),"")</f>
+        <v>386840</v>
+      </c>
+      <c r="C3" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A3,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B4" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A4,平日!$A$2:$A$71,0)),"")</f>
+        <v>377840</v>
+      </c>
+      <c r="C4" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A4,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B5" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A5,平日!$A$2:$A$71,0)),"")</f>
+        <v>428620</v>
+      </c>
+      <c r="C5" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A5,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A6,平日!$A$2:$A$71,0)),"")</f>
+        <v>374210</v>
+      </c>
+      <c r="C6" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A6,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B7" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A7,平日!$A$2:$A$71,0)),"")</f>
+        <v>459300</v>
+      </c>
+      <c r="C7" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A7,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B8" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A8,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A8,土日!$A$2:$A$28,0)),"")</f>
+        <v>716170</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B9" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A9,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A9,土日!$A$2:$A$28,0)),"")</f>
+        <v>707360</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B10" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A10,平日!$A$2:$A$71,0)),"")</f>
+        <v>335720</v>
+      </c>
+      <c r="C10" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A10,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B11" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A11,平日!$A$2:$A$71,0)),"")</f>
+        <v>304420</v>
+      </c>
+      <c r="C11" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A11,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B12" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A12,平日!$A$2:$A$71,0)),"")</f>
+        <v>454040</v>
+      </c>
+      <c r="C12" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A12,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B13" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A13,平日!$A$2:$A$71,0)),"")</f>
+        <v>421760</v>
+      </c>
+      <c r="C13" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A13,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="30" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B14" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A14,平日!$A$2:$A$71,0)),"")</f>
+        <v>526640</v>
+      </c>
+      <c r="C14" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A14,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B15" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A15,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A15,土日!$A$2:$A$28,0)),"")</f>
+        <v>833600</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B16" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A16,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A16,土日!$A$2:$A$28,0)),"")</f>
+        <v>717490</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B17" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A17,平日!$A$2:$A$71,0)),"")</f>
+        <v>294280</v>
+      </c>
+      <c r="C17" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A17,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B18" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A18,平日!$A$2:$A$71,0)),"")</f>
+        <v>332760</v>
+      </c>
+      <c r="C18" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A18,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B19" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A19,平日!$A$2:$A$71,0)),"")</f>
+        <v>375800</v>
+      </c>
+      <c r="C19" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A19,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B20" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A20,平日!$A$2:$A$71,0)),"")</f>
+        <v>425290</v>
+      </c>
+      <c r="C20" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A20,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B21" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A21,平日!$A$2:$A$71,0)),"")</f>
+        <v>474820</v>
+      </c>
+      <c r="C21" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A21,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B22" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A22,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A22,土日!$A$2:$A$28,0)),"")</f>
+        <v>773400</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B23" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A23,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A23,土日!$A$2:$A$28,0)),"")</f>
+        <v>786550</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B24" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A24,平日!$A$2:$A$71,0)),"")</f>
+        <v>372650</v>
+      </c>
+      <c r="C24" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A24,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B25" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A25,平日!$A$2:$A$71,0)),"")</f>
+        <v>289840</v>
+      </c>
+      <c r="C25" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A25,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A26,平日!$A$2:$A$71,0)),"")</f>
+        <v>418780</v>
+      </c>
+      <c r="C26" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A26,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B27" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A27,平日!$A$2:$A$71,0)),"")</f>
+        <v>459900</v>
+      </c>
+      <c r="C27" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A27,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B28" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A28,平日!$A$2:$A$71,0)),"")</f>
+        <v>493180</v>
+      </c>
+      <c r="C28" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A28,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B29" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A29,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A29,土日!$A$2:$A$28,0)),"")</f>
+        <v>652640</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B30" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A30,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A30,土日!$A$2:$A$28,0)),"")</f>
+        <v>737850</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="30" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B31" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A31,平日!$A$2:$A$71,0)),"")</f>
+        <v>597070</v>
+      </c>
+      <c r="C31" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A31,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="30" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B32" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A32,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A32,土日!$A$2:$A$28,0)),"")</f>
+        <v>615300</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="30" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B33" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A33,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A33,土日!$A$2:$A$28,0)),"")</f>
+        <v>695890</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="30" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B34" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A34,平日!$A$2:$A$71,0)),"")</f>
+        <v>395610</v>
+      </c>
+      <c r="C34" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A34,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="30" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B35" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A35,平日!$A$2:$A$71,0)),"")</f>
+        <v>357540</v>
+      </c>
+      <c r="C35" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A35,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="30" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B36" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A36,平日!$A$2:$A$71,0)),"")</f>
+        <v>383270</v>
+      </c>
+      <c r="C36" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A36,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="30" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B37" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A37,平日!$A$2:$A$71,0)),"")</f>
+        <v>397380</v>
+      </c>
+      <c r="C37" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A37,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="30" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A38,平日!$A$2:$A$71,0)),"")</f>
+        <v>533650</v>
+      </c>
+      <c r="C38" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A38,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="30" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B39" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A39,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A39,土日!$A$2:$A$28,0)),"")</f>
+        <v>664790</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="30" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B40" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A40,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A40,土日!$A$2:$A$28,0)),"")</f>
+        <v>711580</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="30" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B41" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A41,平日!$A$2:$A$71,0)),"")</f>
+        <v>363910</v>
+      </c>
+      <c r="C41" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A41,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="30" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B42" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A42,平日!$A$2:$A$71,0)),"")</f>
+        <v>360990</v>
+      </c>
+      <c r="C42" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A42,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="30" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B43" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A43,平日!$A$2:$A$71,0)),"")</f>
+        <v>383160</v>
+      </c>
+      <c r="C43" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A43,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="30" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B44" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A44,平日!$A$2:$A$71,0)),"")</f>
+        <v>388830</v>
+      </c>
+      <c r="C44" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A44,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="30" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B45" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A45,平日!$A$2:$A$71,0)),"")</f>
+        <v>449020</v>
+      </c>
+      <c r="C45" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A45,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="30" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B46" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A46,平日!$A$2:$A$71,0)),"")</f>
+        <v>268730</v>
+      </c>
+      <c r="C46" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A46,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="30" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B47" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A47,平日!$A$2:$A$71,0)),"")</f>
+        <v>256280</v>
+      </c>
+      <c r="C47" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A47,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="30" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B48" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A48,平日!$A$2:$A$71,0)),"")</f>
+        <v>351140</v>
+      </c>
+      <c r="C48" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A48,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="30" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B49" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A49,平日!$A$2:$A$71,0)),"")</f>
+        <v>299580</v>
+      </c>
+      <c r="C49" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A49,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="30" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B50" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A50,平日!$A$2:$A$71,0)),"")</f>
+        <v>362970</v>
+      </c>
+      <c r="C50" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A50,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="30" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B51" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A51,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A51,土日!$A$2:$A$28,0)),"")</f>
+        <v>554810</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="30" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B52" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A52,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A52,土日!$A$2:$A$28,0)),"")</f>
+        <v>477270</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="30" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B53" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A53,平日!$A$2:$A$71,0)),"")</f>
+        <v>219670</v>
+      </c>
+      <c r="C53" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A53,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="30" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B54" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A54,平日!$A$2:$A$71,0)),"")</f>
+        <v>228460</v>
+      </c>
+      <c r="C54" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A54,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="30" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B55" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A55,平日!$A$2:$A$71,0)),"")</f>
+        <v>214940</v>
+      </c>
+      <c r="C55" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A55,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="30" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B56" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A56,平日!$A$2:$A$71,0)),"")</f>
+        <v>263030</v>
+      </c>
+      <c r="C56" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A56,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="30" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B57" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A57,平日!$A$2:$A$71,0)),"")</f>
+        <v>212930</v>
+      </c>
+      <c r="C57" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A57,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="30" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B58" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A58,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A58,土日!$A$2:$A$28,0)),"")</f>
+        <v>573870</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="30" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B59" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A59,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A59,土日!$A$2:$A$28,0)),"")</f>
+        <v>543590</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="30" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B60" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A60,平日!$A$2:$A$71,0)),"")</f>
+        <v>207730</v>
+      </c>
+      <c r="C60" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A60,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="30" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B61" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A61,平日!$A$2:$A$71,0)),"")</f>
+        <v>335170</v>
+      </c>
+      <c r="C61" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A61,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="30" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B62" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A62,平日!$A$2:$A$71,0)),"")</f>
+        <v>212760</v>
+      </c>
+      <c r="C62" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A62,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="30" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B63" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A63,平日!$A$2:$A$71,0)),"")</f>
+        <v>294500</v>
+      </c>
+      <c r="C63" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A63,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="30" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B64" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A64,平日!$A$2:$A$71,0)),"")</f>
+        <v>320850</v>
+      </c>
+      <c r="C64" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A64,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="30" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B65" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A65,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A65,土日!$A$2:$A$28,0)),"")</f>
+        <v>507490</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="30" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B66" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A66,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A66,土日!$A$2:$A$28,0)),"")</f>
+        <v>543290</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="30" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B67" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A67,平日!$A$2:$A$71,0)),"")</f>
+        <v>215510</v>
+      </c>
+      <c r="C67" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A67,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="30" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B68" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A68,平日!$A$2:$A$71,0)),"")</f>
+        <v>167060</v>
+      </c>
+      <c r="C68" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A68,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="30" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B69" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A69,平日!$A$2:$A$71,0)),"")</f>
+        <v>392050</v>
+      </c>
+      <c r="C69" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A69,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="30" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B70" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A70,平日!$A$2:$A$71,0)),"")</f>
+        <v>259100</v>
+      </c>
+      <c r="C70" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A70,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="30" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B71" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A71,平日!$A$2:$A$71,0)),"")</f>
+        <v>278990</v>
+      </c>
+      <c r="C71" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A71,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="30" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B72" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A72,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A72,土日!$A$2:$A$28,0)),"")</f>
+        <v>466800</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="30" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B73" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A73,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C73" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A73,土日!$A$2:$A$28,0)),"")</f>
+        <v>586850</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="30" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B74" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A74,平日!$A$2:$A$71,0)),"")</f>
+        <v>606440</v>
+      </c>
+      <c r="C74" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A74,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="30" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B75" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A75,平日!$A$2:$A$71,0)),"")</f>
+        <v>471650</v>
+      </c>
+      <c r="C75" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A75,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="30" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B76" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A76,平日!$A$2:$A$71,0)),"")</f>
+        <v>425490</v>
+      </c>
+      <c r="C76" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A76,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="30" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B77" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A77,平日!$A$2:$A$71,0)),"")</f>
+        <v>223490</v>
+      </c>
+      <c r="C77" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A77,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="30" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B78" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A78,平日!$A$2:$A$71,0)),"")</f>
+        <v>235170</v>
+      </c>
+      <c r="C78" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A78,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="30" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B79" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A79,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A79,土日!$A$2:$A$28,0)),"")</f>
+        <v>569450</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="30" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B80" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A80,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A80,土日!$A$2:$A$28,0)),"")</f>
+        <v>512050</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="30" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B81" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A81,平日!$A$2:$A$71,0)),"")</f>
+        <v>175910</v>
+      </c>
+      <c r="C81" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A81,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="30" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B82" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A82,平日!$A$2:$A$71,0)),"")</f>
+        <v>203590</v>
+      </c>
+      <c r="C82" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A82,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="30" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B83" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A83,平日!$A$2:$A$71,0)),"")</f>
+        <v>204670</v>
+      </c>
+      <c r="C83" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A83,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="30" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B84" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A84,平日!$A$2:$A$71,0)),"")</f>
+        <v>165390</v>
+      </c>
+      <c r="C84" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A84,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="30" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B85" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A85,平日!$A$2:$A$71,0)),"")</f>
+        <v>250680</v>
+      </c>
+      <c r="C85" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A85,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="30" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B86" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A86,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A86,土日!$A$2:$A$28,0)),"")</f>
+        <v>454190</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="30" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B87" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A87,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A87,土日!$A$2:$A$28,0)),"")</f>
+        <v>606680</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="30" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B88" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A88,平日!$A$2:$A$71,0)),"")</f>
+        <v>190960</v>
+      </c>
+      <c r="C88" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A88,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="30" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B89" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A89,平日!$A$2:$A$71,0)),"")</f>
+        <v>237070</v>
+      </c>
+      <c r="C89" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A89,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="30" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B90" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A90,平日!$A$2:$A$71,0)),"")</f>
+        <v>264350</v>
+      </c>
+      <c r="C90" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A90,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="30" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B91" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A91,平日!$A$2:$A$71,0)),"")</f>
+        <v>211130</v>
+      </c>
+      <c r="C91" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A91,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="30" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B92" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A92,平日!$A$2:$A$71,0)),"")</f>
+        <v>247550</v>
+      </c>
+      <c r="C92" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A92,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="30" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B93" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A93,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A93,土日!$A$2:$A$28,0)),"")</f>
+        <v>377970</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="30" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B94" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A94,平日!$A$2:$A$71,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A94,土日!$A$2:$A$28,0)),"")</f>
+        <v>498390</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="30" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B95" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A95,平日!$A$2:$A$71,0)),"")</f>
+        <v>344250</v>
+      </c>
+      <c r="C95" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A95,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="30" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B96" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A96,平日!$A$2:$A$71,0)),"")</f>
+        <v>167680</v>
+      </c>
+      <c r="C96" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A96,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="30" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B97" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A97,平日!$A$2:$A$71,0)),"")</f>
+        <v>241620</v>
+      </c>
+      <c r="C97" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A97,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="30" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B98" s="31" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A98,平日!$A$2:$A$71,0)),"")</f>
+        <v>213180</v>
+      </c>
+      <c r="C98" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A98,土日!$A$2:$A$28,0)),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/output/売上表_平日土日別.xlsx
+++ b/output/売上表_平日土日別.xlsx
@@ -13,6 +13,7 @@
     <sheet name="平日" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="土日" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="日別推移データ" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="週別データ" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="69">
   <si>
     <r>
       <rPr>
@@ -1168,6 +1169,182 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→ 平日・土日とも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月がピークで、その後は毎月下がっています。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※月曜始まりの週ごとの平均（横軸は週の月曜日）。平日・土日どちらかの報告がない週（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週）は除いています。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※7/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週の平日が高いのは祝日（海の日・敬老の日など）を含むため。</t>
     </r>
   </si>
   <si>
@@ -1272,12 +1449,336 @@
   <si>
     <t xml:space="preserve">土日</t>
   </si>
+  <si>
+    <t xml:space="preserve">週（月曜）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">週の終わり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラフ用ラベル</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6/22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6/29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※平日・土日のどちらかの報告がない週は除外：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0\日"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
@@ -1287,6 +1788,7 @@
     <numFmt numFmtId="170" formatCode="#,##0,,&quot;百万&quot;"/>
     <numFmt numFmtId="171" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="172" formatCode="m/d"/>
+    <numFmt numFmtId="173" formatCode="m/d\週"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1498,7 +2000,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1624,6 +2126,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1948,11 +2458,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-8"/>
-        <c:axId val="86558956"/>
-        <c:axId val="28011317"/>
+        <c:axId val="45006421"/>
+        <c:axId val="93800221"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86558956"/>
+        <c:axId val="45006421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1984,7 +2494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28011317"/>
+        <c:crossAx val="93800221"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1992,7 +2502,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28011317"/>
+        <c:axId val="93800221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2032,7 +2542,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86558956"/>
+        <c:crossAx val="45006421"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2337,11 +2847,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="8612957"/>
-        <c:axId val="4836804"/>
+        <c:axId val="48371873"/>
+        <c:axId val="82728263"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8612957"/>
+        <c:axId val="48371873"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2373,7 +2883,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4836804"/>
+        <c:crossAx val="82728263"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2381,7 +2891,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4836804"/>
+        <c:axId val="82728263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2421,7 +2931,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8612957"/>
+        <c:crossAx val="48371873"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3525,11 +4035,11 @@
         </c:ser>
         <c:gapWidth val="30"/>
         <c:overlap val="100"/>
-        <c:axId val="21385023"/>
-        <c:axId val="13427211"/>
+        <c:axId val="76562719"/>
+        <c:axId val="10023584"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21385023"/>
+        <c:axId val="76562719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3561,7 +4071,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13427211"/>
+        <c:crossAx val="10023584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3569,7 +4079,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13427211"/>
+        <c:axId val="10023584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3609,7 +4119,920 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21385023"/>
+        <c:crossAx val="76562719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>④ 1日平均売上の推移・月別（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"平日 1日平均"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 1日平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="2a78d6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2a78d6"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>月別集計!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>月別集計!$D$4:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>380992.857142857</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>421276.842105263</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>336752.727272727</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>279522.272727273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>230350.909090909</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"土日 1日平均"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 1日平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="eb6834"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="eb6834"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>月別集計!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>月別集計!$G$4:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>686633.333333333</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>726590</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>602112.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>537923.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>484307.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="6092702"/>
+        <c:axId val="14756252"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="6092702"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="14756252"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="14756252"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="800000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="6092702"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>⑤ 1日平均売上の推移・週別（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>週別データ!C1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 1日平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="2a78d6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2a78d6"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>週別データ!$E$2:$E$14</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>6/22週</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/29週</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7/6週</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7/13週</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7/20週</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7/27週</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8/24週</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8/31週</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9/7週</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9/14週</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9/21週</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9/28週</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10/5週</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>週別データ!$C$2:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>405362</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>408516</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>380590</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>406870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>597070</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>413490</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>307740</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>227806</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>274202</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>262542</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>392448</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>200048</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>230212</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>週別データ!D1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 1日平均</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="eb6834"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="eb6834"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>週別データ!$E$2:$E$14</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>6/22週</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/29週</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7/6週</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7/13週</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7/20週</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7/27週</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8/24週</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8/31週</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9/7週</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9/14週</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9/21週</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9/28週</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10/5週</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>週別データ!$D$2:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>711765</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>775545</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>779975</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>695245</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>655595</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>688185</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>516040</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>558730</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>525390</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>526825</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>540750</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>530435</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>438180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="287479"/>
+        <c:axId val="83831011"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="287479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="bfbfbf"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="83831011"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="83831011"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,\千" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="287479"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3748,6 +5171,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>2520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>364680</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="12192120"/>
+        <a:ext cx="6479640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>13320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>403920</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>183960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="16002000"/>
+        <a:ext cx="10799640" cy="3599640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4266,7 +5749,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4292,6 +5775,21 @@
     <row r="63" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="17" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4324,22 +5822,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4354,7 +5852,7 @@
         <v>386840</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -4371,7 +5869,7 @@
         <v>377840</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -4388,7 +5886,7 @@
         <v>428620</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -4405,7 +5903,7 @@
         <v>374210</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -4422,7 +5920,7 @@
         <v>459300</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4439,7 +5937,7 @@
         <v>335720</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4456,7 +5954,7 @@
         <v>304420</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -4473,7 +5971,7 @@
         <v>454040</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -4490,7 +5988,7 @@
         <v>421760</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -4507,7 +6005,7 @@
         <v>526640</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -4524,7 +6022,7 @@
         <v>294280</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -4541,7 +6039,7 @@
         <v>332760</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -4558,7 +6056,7 @@
         <v>375800</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -4575,7 +6073,7 @@
         <v>425290</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -4592,7 +6090,7 @@
         <v>474820</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -4609,7 +6107,7 @@
         <v>372650</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -4626,7 +6124,7 @@
         <v>289840</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -4643,7 +6141,7 @@
         <v>418780</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -4660,7 +6158,7 @@
         <v>459900</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -4677,7 +6175,7 @@
         <v>493180</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -4694,10 +6192,10 @@
         <v>597070</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F22" s="5"/>
     </row>
@@ -4713,7 +6211,7 @@
         <v>395610</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -4730,7 +6228,7 @@
         <v>357540</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -4747,7 +6245,7 @@
         <v>383270</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -4764,7 +6262,7 @@
         <v>397380</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -4781,7 +6279,7 @@
         <v>533650</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -4798,7 +6296,7 @@
         <v>363910</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -4815,7 +6313,7 @@
         <v>360990</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -4832,7 +6330,7 @@
         <v>383160</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -4849,7 +6347,7 @@
         <v>388830</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -4866,7 +6364,7 @@
         <v>449020</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -4883,7 +6381,7 @@
         <v>268730</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -4900,7 +6398,7 @@
         <v>256280</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -4917,7 +6415,7 @@
         <v>351140</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -4934,7 +6432,7 @@
         <v>299580</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -4951,7 +6449,7 @@
         <v>362970</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -4968,7 +6466,7 @@
         <v>219670</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -4985,7 +6483,7 @@
         <v>228460</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -5002,7 +6500,7 @@
         <v>214940</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -5019,7 +6517,7 @@
         <v>263030</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -5036,7 +6534,7 @@
         <v>212930</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -5053,7 +6551,7 @@
         <v>207730</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -5070,7 +6568,7 @@
         <v>335170</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -5087,7 +6585,7 @@
         <v>212760</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -5104,7 +6602,7 @@
         <v>294500</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -5121,7 +6619,7 @@
         <v>320850</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -5138,7 +6636,7 @@
         <v>215510</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -5155,7 +6653,7 @@
         <v>167060</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -5172,7 +6670,7 @@
         <v>392050</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -5189,7 +6687,7 @@
         <v>259100</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
@@ -5206,7 +6704,7 @@
         <v>278990</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
@@ -5223,10 +6721,10 @@
         <v>606440</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F53" s="5"/>
     </row>
@@ -5242,10 +6740,10 @@
         <v>471650</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F54" s="5"/>
     </row>
@@ -5261,10 +6759,10 @@
         <v>425490</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F55" s="5"/>
     </row>
@@ -5280,7 +6778,7 @@
         <v>223490</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -5297,7 +6795,7 @@
         <v>235170</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -5314,7 +6812,7 @@
         <v>175910</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
@@ -5331,7 +6829,7 @@
         <v>203590</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
@@ -5348,7 +6846,7 @@
         <v>204670</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
@@ -5365,7 +6863,7 @@
         <v>165390</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
@@ -5382,7 +6880,7 @@
         <v>250680</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
@@ -5399,7 +6897,7 @@
         <v>190960</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
@@ -5416,7 +6914,7 @@
         <v>237070</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
@@ -5433,7 +6931,7 @@
         <v>264350</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
@@ -5450,7 +6948,7 @@
         <v>211130</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
@@ -5467,7 +6965,7 @@
         <v>247550</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
@@ -5484,10 +6982,10 @@
         <v>344250</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F68" s="5"/>
     </row>
@@ -5503,7 +7001,7 @@
         <v>167680</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
@@ -5520,7 +7018,7 @@
         <v>241620</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
@@ -5537,7 +7035,7 @@
         <v>213180</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
@@ -5553,7 +7051,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C73" s="15" t="n">
         <f aca="false">COUNT(C2:C71)</f>
@@ -5562,7 +7060,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C74" s="24" t="n">
         <f aca="false">IF(C73=0,0,C72/C73)</f>
@@ -5598,22 +7096,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5628,7 +7126,7 @@
         <v>636370</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -5645,7 +7143,7 @@
         <v>716170</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -5662,7 +7160,7 @@
         <v>707360</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -5679,7 +7177,7 @@
         <v>833600</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -5696,7 +7194,7 @@
         <v>717490</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -5713,7 +7211,7 @@
         <v>773400</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -5730,7 +7228,7 @@
         <v>786550</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -5747,7 +7245,7 @@
         <v>652640</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -5764,7 +7262,7 @@
         <v>737850</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -5781,7 +7279,7 @@
         <v>615300</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -5798,11 +7296,11 @@
         <v>695890</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="23" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5817,7 +7315,7 @@
         <v>664790</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -5834,7 +7332,7 @@
         <v>711580</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -5851,7 +7349,7 @@
         <v>554810</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -5868,7 +7366,7 @@
         <v>477270</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -5885,7 +7383,7 @@
         <v>573870</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -5902,7 +7400,7 @@
         <v>543590</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -5919,7 +7417,7 @@
         <v>507490</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -5936,7 +7434,7 @@
         <v>543290</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -5953,7 +7451,7 @@
         <v>466800</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -5970,7 +7468,7 @@
         <v>586850</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -5987,7 +7485,7 @@
         <v>569450</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -6004,7 +7502,7 @@
         <v>512050</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -6021,7 +7519,7 @@
         <v>454190</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -6038,7 +7536,7 @@
         <v>606680</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -6055,7 +7553,7 @@
         <v>377970</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -6072,7 +7570,7 @@
         <v>498390</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -6088,7 +7586,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">COUNT(C2:C28)</f>
@@ -6097,7 +7595,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C31" s="24" t="n">
         <f aca="false">IF(C30=0,0,C29/C30)</f>
@@ -6129,13 +7627,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7397,6 +8895,312 @@
       <c r="C98" s="31" t="str">
         <f aca="false">IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A98,土日!$A$2:$A$28,0)),"")</f>
         <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2" s="33" t="n">
+        <f aca="false">A2+6</f>
+        <v>46201</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A2,平日!$A$2:$A$71,"&lt;="&amp;B2)</f>
+        <v>405362</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A2,土日!$A$2:$A$28,"&lt;="&amp;B2)</f>
+        <v>711765</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B3" s="33" t="n">
+        <f aca="false">A3+6</f>
+        <v>46208</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A3,平日!$A$2:$A$71,"&lt;="&amp;B3)</f>
+        <v>408516</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A3,土日!$A$2:$A$28,"&lt;="&amp;B3)</f>
+        <v>775545</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B4" s="33" t="n">
+        <f aca="false">A4+6</f>
+        <v>46215</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A4,平日!$A$2:$A$71,"&lt;="&amp;B4)</f>
+        <v>380590</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A4,土日!$A$2:$A$28,"&lt;="&amp;B4)</f>
+        <v>779975</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="32" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B5" s="33" t="n">
+        <f aca="false">A5+6</f>
+        <v>46222</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A5,平日!$A$2:$A$71,"&lt;="&amp;B5)</f>
+        <v>406870</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A5,土日!$A$2:$A$28,"&lt;="&amp;B5)</f>
+        <v>695245</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B6" s="33" t="n">
+        <f aca="false">A6+6</f>
+        <v>46229</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A6,平日!$A$2:$A$71,"&lt;="&amp;B6)</f>
+        <v>597070</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A6,土日!$A$2:$A$28,"&lt;="&amp;B6)</f>
+        <v>655595</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="32" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B7" s="33" t="n">
+        <f aca="false">A7+6</f>
+        <v>46236</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A7,平日!$A$2:$A$71,"&lt;="&amp;B7)</f>
+        <v>413490</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A7,土日!$A$2:$A$28,"&lt;="&amp;B7)</f>
+        <v>688185</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B8" s="33" t="n">
+        <f aca="false">A8+6</f>
+        <v>46264</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A8,平日!$A$2:$A$71,"&lt;="&amp;B8)</f>
+        <v>307740</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A8,土日!$A$2:$A$28,"&lt;="&amp;B8)</f>
+        <v>516040</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B9" s="33" t="n">
+        <f aca="false">A9+6</f>
+        <v>46271</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A9,平日!$A$2:$A$71,"&lt;="&amp;B9)</f>
+        <v>227806</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A9,土日!$A$2:$A$28,"&lt;="&amp;B9)</f>
+        <v>558730</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="33" t="n">
+        <f aca="false">A10+6</f>
+        <v>46278</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A10,平日!$A$2:$A$71,"&lt;="&amp;B10)</f>
+        <v>274202</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A10,土日!$A$2:$A$28,"&lt;="&amp;B10)</f>
+        <v>525390</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B11" s="33" t="n">
+        <f aca="false">A11+6</f>
+        <v>46285</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A11,平日!$A$2:$A$71,"&lt;="&amp;B11)</f>
+        <v>262542</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A11,土日!$A$2:$A$28,"&lt;="&amp;B11)</f>
+        <v>526825</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B12" s="33" t="n">
+        <f aca="false">A12+6</f>
+        <v>46292</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A12,平日!$A$2:$A$71,"&lt;="&amp;B12)</f>
+        <v>392448</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A12,土日!$A$2:$A$28,"&lt;="&amp;B12)</f>
+        <v>540750</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B13" s="33" t="n">
+        <f aca="false">A13+6</f>
+        <v>46299</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A13,平日!$A$2:$A$71,"&lt;="&amp;B13)</f>
+        <v>200048</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A13,土日!$A$2:$A$28,"&lt;="&amp;B13)</f>
+        <v>530435</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B14" s="33" t="n">
+        <f aca="false">A14+6</f>
+        <v>46306</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <f aca="false">AVERAGEIFS(平日!$C$2:$C$71,平日!$A$2:$A$71,"&gt;="&amp;A14,平日!$A$2:$A$71,"&lt;="&amp;B14)</f>
+        <v>230212</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <f aca="false">AVERAGEIFS(土日!$C$2:$C$28,土日!$A$2:$A$28,"&gt;="&amp;A14,土日!$A$2:$A$28,"&lt;="&amp;B14)</f>
+        <v>438180</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/output/売上表_平日土日別.xlsx
+++ b/output/売上表_平日土日別.xlsx
@@ -14,6 +14,10 @@
     <sheet name="土日" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="日別推移データ" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="週別データ" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="7月" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="8月" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="9月" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="10月" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="88">
   <si>
     <r>
       <rPr>
@@ -1773,6 +1777,443 @@
       <t xml:space="preserve">週</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 日別売上（平日・土日別）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">区分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平日 売上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土日 売上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月間サマリー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業日数（報告あり）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最低</t>
+  </si>
+  <si>
+    <t xml:space="preserve">構成比</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">土日</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平日（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日平均）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">報告なしの日数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※7/26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は訂正後の値（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">695,890</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は海の日（平日扱い）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 日別売上（平日・土日別）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※8/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は報告なしのため合計は実際より少なめ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 日別売上（平日・土日別）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※9/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">敬老の日・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">国民の休日・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秋分の日は平日扱い。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 日別売上（平日・土日別）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※10/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">までの集計。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スポーツの日は平日扱い。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1790,7 +2231,7 @@
     <numFmt numFmtId="172" formatCode="m/d"/>
     <numFmt numFmtId="173" formatCode="m/d\週"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1918,8 +2359,20 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1948,6 +2401,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
         <bgColor rgb="FFE3E2DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDEBE3"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -2000,7 +2459,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2137,6 +2596,58 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2150,7 +2661,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -2166,8 +2677,8 @@
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFDEBE3"/>
       <rgbColor rgb="FFE7E6E6"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -2458,11 +2969,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-8"/>
-        <c:axId val="45006421"/>
-        <c:axId val="93800221"/>
+        <c:axId val="34001219"/>
+        <c:axId val="89504468"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45006421"/>
+        <c:axId val="34001219"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2494,7 +3005,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93800221"/>
+        <c:crossAx val="89504468"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2502,7 +3013,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93800221"/>
+        <c:axId val="89504468"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2542,7 +3053,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45006421"/>
+        <c:crossAx val="34001219"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2847,11 +3358,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="48371873"/>
-        <c:axId val="82728263"/>
+        <c:axId val="58443189"/>
+        <c:axId val="96269336"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48371873"/>
+        <c:axId val="58443189"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2883,7 +3394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82728263"/>
+        <c:crossAx val="96269336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2891,7 +3402,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82728263"/>
+        <c:axId val="96269336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2931,7 +3442,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48371873"/>
+        <c:crossAx val="58443189"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4035,11 +4546,11 @@
         </c:ser>
         <c:gapWidth val="30"/>
         <c:overlap val="100"/>
-        <c:axId val="76562719"/>
-        <c:axId val="10023584"/>
+        <c:axId val="13123281"/>
+        <c:axId val="15056738"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76562719"/>
+        <c:axId val="13123281"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4071,7 +4582,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10023584"/>
+        <c:crossAx val="15056738"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4079,7 +4590,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10023584"/>
+        <c:axId val="15056738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4119,7 +4630,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76562719"/>
+        <c:crossAx val="13123281"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4447,11 +4958,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="6092702"/>
-        <c:axId val="14756252"/>
+        <c:axId val="60470986"/>
+        <c:axId val="86648097"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6092702"/>
+        <c:axId val="60470986"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4483,7 +4994,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14756252"/>
+        <c:crossAx val="86648097"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4491,7 +5002,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14756252"/>
+        <c:axId val="86648097"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="800000"/>
@@ -4532,7 +5043,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6092702"/>
+        <c:crossAx val="60470986"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4948,11 +5459,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="287479"/>
-        <c:axId val="83831011"/>
+        <c:axId val="26314638"/>
+        <c:axId val="16879119"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="287479"/>
+        <c:axId val="26314638"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4984,7 +5495,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83831011"/>
+        <c:crossAx val="16879119"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4992,7 +5503,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83831011"/>
+        <c:axId val="16879119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -5032,7 +5543,2174 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="287479"/>
+        <c:crossAx val="26314638"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>7月 日別売上（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>7月!G3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>7月!$A$4:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>7/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7/30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7/31</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>7月!$G$4:$G$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>454040</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>421760</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>526640</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>294280</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>332760</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>375800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>425290</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>474820</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>372650</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>289840</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>418780</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>459900</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>493180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>597070</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>395610</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>357540</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>383270</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>397380</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>533650</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>7月!H3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>7月!$A$4:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>7/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7/30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7/31</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>7月!$H$4:$H$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="3">
+                  <c:v>833600</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>717490</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>773400</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>786550</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>652640</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>737850</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>615300</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>695890</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="40"/>
+        <c:overlap val="100"/>
+        <c:axId val="93300027"/>
+        <c:axId val="55087540"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="93300027"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="55087540"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="55087540"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,\千" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="93300027"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>8月 日別売上（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>8月!G3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>8月!$A$4:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>8/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8/30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8/31</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>8月!$G$4:$G$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="2">
+                  <c:v>363910</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>360990</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>383160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>388830</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>449020</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>268730</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>256280</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>351140</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>299580</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>362970</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>219670</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>8月!H3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>8月!$A$4:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>8/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8/30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8/31</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>8月!$H$4:$H$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>664790</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>711580</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>554810</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>477270</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="40"/>
+        <c:overlap val="100"/>
+        <c:axId val="95922708"/>
+        <c:axId val="61789660"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="95922708"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="61789660"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="61789660"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,\千" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="95922708"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>9月 日別売上（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>9月!G3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>9月!$A$4:$A$33</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>9/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9/30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>9月!$G$4:$G$33</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>228460</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>214940</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>263030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>212930</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>207730</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>335170</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>212760</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>294500</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>320850</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>215510</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>167060</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>392050</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>259100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>278990</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>606440</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>471650</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>425490</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>223490</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>235170</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>175910</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>203590</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>204670</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>9月!H3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>9月!$A$4:$A$33</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>9/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9/30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>9月!$H$4:$H$33</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="4">
+                  <c:v>573870</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>543590</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>507490</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>543290</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>466800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>586850</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>569450</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>512050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="40"/>
+        <c:overlap val="100"/>
+        <c:axId val="66498381"/>
+        <c:axId val="33355366"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="66498381"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="33355366"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="33355366"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,\千" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="66498381"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>10月 日別売上（円）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>10月!G3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2a78d6"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>10月!$A$4:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>10/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10/15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>10月!$G$4:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>165390</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250680</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>190960</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>237070</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>264350</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>211130</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>247550</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>344250</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>167680</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>241620</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>213180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>10月!H3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土日 売上</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="eb6834"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>10月!$A$4:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>10/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10/15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>10月!$H$4:$H$18</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="2">
+                  <c:v>454190</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>606680</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>377970</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>498390</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="40"/>
+        <c:overlap val="100"/>
+        <c:axId val="49884805"/>
+        <c:axId val="93523744"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="49884805"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="93523744"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="93523744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="e3e2de"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0,\千" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="49884805"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5239,6 +7917,146 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>595080</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>135720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6202800" y="2666880"/>
+        <a:ext cx="7199640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>595080</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>135720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6202800" y="2666880"/>
+        <a:ext cx="7199640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>595080</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>135720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6202800" y="2666880"/>
+        <a:ext cx="7199640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>595080</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>135720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6202800" y="2666880"/>
+        <a:ext cx="7199640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -5744,6 +8562,641 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A4),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C4" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A4)=1,WEEKDAY(A4)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A4,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A4,土日!$A$2:$A$28,0)),""))</f>
+        <v>165390</v>
+      </c>
+      <c r="F4" s="5" t="str">
+        <f aca="false">IF(E4="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A4,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A4,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <f aca="false">IF(AND(C4="平日",E4&lt;&gt;""),E4,"")</f>
+        <v>165390</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f aca="false">IF(AND(C4="土日",E4&lt;&gt;""),E4,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="35"/>
+      <c r="K4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B5" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A5),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C5" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A5)=1,WEEKDAY(A5)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A5,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A5,土日!$A$2:$A$28,0)),""))</f>
+        <v>250680</v>
+      </c>
+      <c r="F5" s="5" t="str">
+        <f aca="false">IF(E5="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A5,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A5,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <f aca="false">IF(AND(C5="平日",E5&lt;&gt;""),E5,"")</f>
+        <v>250680</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f aca="false">IF(AND(C5="土日",E5&lt;&gt;""),E5,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <f aca="false">SUM(G4:G18)</f>
+        <v>2533860</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <f aca="false">SUM(H4:H18)</f>
+        <v>1937230</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <f aca="false">K5+L5</f>
+        <v>4471090</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="38" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B6" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A6),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C6" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A6)=1,WEEKDAY(A6)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A6,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A6,土日!$A$2:$A$28,0)),""))</f>
+        <v>454190</v>
+      </c>
+      <c r="F6" s="40" t="str">
+        <f aca="false">IF(E6="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A6,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A6,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G6" s="41" t="str">
+        <f aca="false">IF(AND(C6="平日",E6&lt;&gt;""),E6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="41" t="n">
+        <f aca="false">IF(AND(C6="土日",E6&lt;&gt;""),E6,"")</f>
+        <v>454190</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <f aca="false">COUNT(G4:G18)</f>
+        <v>11</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <f aca="false">COUNT(H4:H18)</f>
+        <v>4</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <f aca="false">K6+L6</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="38" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B7" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A7),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C7" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A7)=1,WEEKDAY(A7)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A7,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A7,土日!$A$2:$A$28,0)),""))</f>
+        <v>606680</v>
+      </c>
+      <c r="F7" s="40" t="str">
+        <f aca="false">IF(E7="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A7,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A7,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G7" s="41" t="str">
+        <f aca="false">IF(AND(C7="平日",E7&lt;&gt;""),E7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="41" t="n">
+        <f aca="false">IF(AND(C7="土日",E7&lt;&gt;""),E7,"")</f>
+        <v>606680</v>
+      </c>
+      <c r="J7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <f aca="false">IF(K6=0,0,K5/K6)</f>
+        <v>230350.909090909</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <f aca="false">IF(L6=0,0,L5/L6)</f>
+        <v>484307.5</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <f aca="false">IF(M6=0,0,M5/M6)</f>
+        <v>298072.666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B8" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A8),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C8" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A8)=1,WEEKDAY(A8)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A8,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A8,土日!$A$2:$A$28,0)),""))</f>
+        <v>190960</v>
+      </c>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(E8="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A8,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A8,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <f aca="false">IF(AND(C8="平日",E8&lt;&gt;""),E8,"")</f>
+        <v>190960</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f aca="false">IF(AND(C8="土日",E8&lt;&gt;""),E8,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <f aca="false">MAX(G4:G18)</f>
+        <v>344250</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <f aca="false">MAX(H4:H18)</f>
+        <v>606680</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <f aca="false">MAX(K8:L8)</f>
+        <v>606680</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B9" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A9),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C9" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A9)=1,WEEKDAY(A9)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A9,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A9,土日!$A$2:$A$28,0)),""))</f>
+        <v>237070</v>
+      </c>
+      <c r="F9" s="5" t="str">
+        <f aca="false">IF(E9="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A9,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A9,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <f aca="false">IF(AND(C9="平日",E9&lt;&gt;""),E9,"")</f>
+        <v>237070</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f aca="false">IF(AND(C9="土日",E9&lt;&gt;""),E9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <f aca="false">MIN(G4:G18)</f>
+        <v>165390</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <f aca="false">MIN(H4:H18)</f>
+        <v>377970</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <f aca="false">MIN(K9:L9)</f>
+        <v>165390</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B10" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A10),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C10" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A10)=1,WEEKDAY(A10)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A10,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A10,土日!$A$2:$A$28,0)),""))</f>
+        <v>264350</v>
+      </c>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(E10="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A10,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A10,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <f aca="false">IF(AND(C10="平日",E10&lt;&gt;""),E10,"")</f>
+        <v>264350</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f aca="false">IF(AND(C10="土日",E10&lt;&gt;""),E10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,K5/M5)</f>
+        <v>0.566720866723774</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,L5/M5)</f>
+        <v>0.433279133276226</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <f aca="false">K10+L10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B11" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A11),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C11" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A11)=1,WEEKDAY(A11)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A11,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A11,土日!$A$2:$A$28,0)),""))</f>
+        <v>211130</v>
+      </c>
+      <c r="F11" s="5" t="str">
+        <f aca="false">IF(E11="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A11,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A11,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <f aca="false">IF(AND(C11="平日",E11&lt;&gt;""),E11,"")</f>
+        <v>211130</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <f aca="false">IF(AND(C11="土日",E11&lt;&gt;""),E11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <f aca="false">IF(K7=0,0,L7/K7)</f>
+        <v>2.10247705082364</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B12" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A12),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C12" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A12)=1,WEEKDAY(A12)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A12,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A12,土日!$A$2:$A$28,0)),""))</f>
+        <v>247550</v>
+      </c>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(E12="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A12,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A12,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <f aca="false">IF(AND(C12="平日",E12&lt;&gt;""),E12,"")</f>
+        <v>247550</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f aca="false">IF(AND(C12="土日",E12&lt;&gt;""),E12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="43" t="n">
+        <f aca="false">COUNTIF(F4:F18,"報告なし")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="38" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B13" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A13),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C13" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A13)=1,WEEKDAY(A13)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A13,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A13,土日!$A$2:$A$28,0)),""))</f>
+        <v>377970</v>
+      </c>
+      <c r="F13" s="40" t="str">
+        <f aca="false">IF(E13="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A13,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A13,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G13" s="41" t="str">
+        <f aca="false">IF(AND(C13="平日",E13&lt;&gt;""),E13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="41" t="n">
+        <f aca="false">IF(AND(C13="土日",E13&lt;&gt;""),E13,"")</f>
+        <v>377970</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="38" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B14" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A14),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C14" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A14)=1,WEEKDAY(A14)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A14,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A14,土日!$A$2:$A$28,0)),""))</f>
+        <v>498390</v>
+      </c>
+      <c r="F14" s="40" t="str">
+        <f aca="false">IF(E14="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A14,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A14,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G14" s="41" t="str">
+        <f aca="false">IF(AND(C14="平日",E14&lt;&gt;""),E14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="n">
+        <f aca="false">IF(AND(C14="土日",E14&lt;&gt;""),E14,"")</f>
+        <v>498390</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B15" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A15),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C15" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A15)=1,WEEKDAY(A15)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A15,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A15,土日!$A$2:$A$28,0)),""))</f>
+        <v>344250</v>
+      </c>
+      <c r="F15" s="5" t="str">
+        <f aca="false">IF(E15="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A15,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A15,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <f aca="false">IF(AND(C15="平日",E15&lt;&gt;""),E15,"")</f>
+        <v>344250</v>
+      </c>
+      <c r="H15" s="7" t="str">
+        <f aca="false">IF(AND(C15="土日",E15&lt;&gt;""),E15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B16" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A16),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C16" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A16)=1,WEEKDAY(A16)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A16,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A16,土日!$A$2:$A$28,0)),""))</f>
+        <v>167680</v>
+      </c>
+      <c r="F16" s="5" t="str">
+        <f aca="false">IF(E16="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A16,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A16,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <f aca="false">IF(AND(C16="平日",E16&lt;&gt;""),E16,"")</f>
+        <v>167680</v>
+      </c>
+      <c r="H16" s="7" t="str">
+        <f aca="false">IF(AND(C16="土日",E16&lt;&gt;""),E16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B17" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A17),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C17" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A17)=1,WEEKDAY(A17)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A17,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A17,土日!$A$2:$A$28,0)),""))</f>
+        <v>241620</v>
+      </c>
+      <c r="F17" s="5" t="str">
+        <f aca="false">IF(E17="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A17,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A17,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <f aca="false">IF(AND(C17="平日",E17&lt;&gt;""),E17,"")</f>
+        <v>241620</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <f aca="false">IF(AND(C17="土日",E17&lt;&gt;""),E17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B18" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A18),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C18" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A18)=1,WEEKDAY(A18)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A18,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A18,土日!$A$2:$A$28,0)),""))</f>
+        <v>213180</v>
+      </c>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(E18="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A18,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A18,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <f aca="false">IF(AND(C18="平日",E18&lt;&gt;""),E18,"")</f>
+        <v>213180</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <f aca="false">IF(AND(C18="土日",E18&lt;&gt;""),E18,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -9212,4 +12665,3321 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B4" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A4),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C4" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A4)=1,WEEKDAY(A4)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A4,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A4,土日!$A$2:$A$28,0)),""))</f>
+        <v>454040</v>
+      </c>
+      <c r="F4" s="5" t="str">
+        <f aca="false">IF(E4="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A4,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A4,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <f aca="false">IF(AND(C4="平日",E4&lt;&gt;""),E4,"")</f>
+        <v>454040</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f aca="false">IF(AND(C4="土日",E4&lt;&gt;""),E4,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="35"/>
+      <c r="K4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B5" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A5),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C5" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A5)=1,WEEKDAY(A5)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A5,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A5,土日!$A$2:$A$28,0)),""))</f>
+        <v>421760</v>
+      </c>
+      <c r="F5" s="5" t="str">
+        <f aca="false">IF(E5="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A5,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A5,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <f aca="false">IF(AND(C5="平日",E5&lt;&gt;""),E5,"")</f>
+        <v>421760</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f aca="false">IF(AND(C5="土日",E5&lt;&gt;""),E5,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <f aca="false">SUM(G4:G34)</f>
+        <v>8004260</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <f aca="false">SUM(H4:H34)</f>
+        <v>5812720</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <f aca="false">K5+L5</f>
+        <v>13816980</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B6" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A6),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C6" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A6)=1,WEEKDAY(A6)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A6,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A6,土日!$A$2:$A$28,0)),""))</f>
+        <v>526640</v>
+      </c>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(E6="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A6,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A6,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <f aca="false">IF(AND(C6="平日",E6&lt;&gt;""),E6,"")</f>
+        <v>526640</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f aca="false">IF(AND(C6="土日",E6&lt;&gt;""),E6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <f aca="false">COUNT(G4:G34)</f>
+        <v>19</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <f aca="false">COUNT(H4:H34)</f>
+        <v>8</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <f aca="false">K6+L6</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="38" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B7" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A7),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C7" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A7)=1,WEEKDAY(A7)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A7,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A7,土日!$A$2:$A$28,0)),""))</f>
+        <v>833600</v>
+      </c>
+      <c r="F7" s="40" t="str">
+        <f aca="false">IF(E7="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A7,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A7,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G7" s="41" t="str">
+        <f aca="false">IF(AND(C7="平日",E7&lt;&gt;""),E7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="41" t="n">
+        <f aca="false">IF(AND(C7="土日",E7&lt;&gt;""),E7,"")</f>
+        <v>833600</v>
+      </c>
+      <c r="J7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <f aca="false">IF(K6=0,0,K5/K6)</f>
+        <v>421276.842105263</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <f aca="false">IF(L6=0,0,L5/L6)</f>
+        <v>726590</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <f aca="false">IF(M6=0,0,M5/M6)</f>
+        <v>511740</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="38" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B8" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A8),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C8" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A8)=1,WEEKDAY(A8)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A8,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A8,土日!$A$2:$A$28,0)),""))</f>
+        <v>717490</v>
+      </c>
+      <c r="F8" s="40" t="str">
+        <f aca="false">IF(E8="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A8,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A8,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G8" s="41" t="str">
+        <f aca="false">IF(AND(C8="平日",E8&lt;&gt;""),E8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="41" t="n">
+        <f aca="false">IF(AND(C8="土日",E8&lt;&gt;""),E8,"")</f>
+        <v>717490</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <f aca="false">MAX(G4:G34)</f>
+        <v>597070</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <f aca="false">MAX(H4:H34)</f>
+        <v>833600</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <f aca="false">MAX(K8:L8)</f>
+        <v>833600</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A9),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C9" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A9)=1,WEEKDAY(A9)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A9,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A9,土日!$A$2:$A$28,0)),""))</f>
+        <v>294280</v>
+      </c>
+      <c r="F9" s="5" t="str">
+        <f aca="false">IF(E9="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A9,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A9,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <f aca="false">IF(AND(C9="平日",E9&lt;&gt;""),E9,"")</f>
+        <v>294280</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f aca="false">IF(AND(C9="土日",E9&lt;&gt;""),E9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <f aca="false">MIN(G4:G34)</f>
+        <v>289840</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <f aca="false">MIN(H4:H34)</f>
+        <v>615300</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <f aca="false">MIN(K9:L9)</f>
+        <v>289840</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B10" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A10),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C10" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A10)=1,WEEKDAY(A10)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A10,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A10,土日!$A$2:$A$28,0)),""))</f>
+        <v>332760</v>
+      </c>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(E10="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A10,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A10,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <f aca="false">IF(AND(C10="平日",E10&lt;&gt;""),E10,"")</f>
+        <v>332760</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f aca="false">IF(AND(C10="土日",E10&lt;&gt;""),E10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,K5/M5)</f>
+        <v>0.579306042275519</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,L5/M5)</f>
+        <v>0.420693957724481</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <f aca="false">K10+L10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B11" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A11),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C11" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A11)=1,WEEKDAY(A11)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A11,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A11,土日!$A$2:$A$28,0)),""))</f>
+        <v>375800</v>
+      </c>
+      <c r="F11" s="5" t="str">
+        <f aca="false">IF(E11="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A11,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A11,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <f aca="false">IF(AND(C11="平日",E11&lt;&gt;""),E11,"")</f>
+        <v>375800</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <f aca="false">IF(AND(C11="土日",E11&lt;&gt;""),E11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <f aca="false">IF(K7=0,0,L7/K7)</f>
+        <v>1.72473282976815</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B12" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A12),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C12" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A12)=1,WEEKDAY(A12)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A12,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A12,土日!$A$2:$A$28,0)),""))</f>
+        <v>425290</v>
+      </c>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(E12="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A12,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A12,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <f aca="false">IF(AND(C12="平日",E12&lt;&gt;""),E12,"")</f>
+        <v>425290</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f aca="false">IF(AND(C12="土日",E12&lt;&gt;""),E12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="43" t="n">
+        <f aca="false">COUNTIF(F4:F34,"報告なし")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B13" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A13),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C13" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A13)=1,WEEKDAY(A13)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A13,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A13,土日!$A$2:$A$28,0)),""))</f>
+        <v>474820</v>
+      </c>
+      <c r="F13" s="5" t="str">
+        <f aca="false">IF(E13="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A13,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A13,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <f aca="false">IF(AND(C13="平日",E13&lt;&gt;""),E13,"")</f>
+        <v>474820</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <f aca="false">IF(AND(C13="土日",E13&lt;&gt;""),E13,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="38" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B14" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A14),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C14" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A14)=1,WEEKDAY(A14)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A14,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A14,土日!$A$2:$A$28,0)),""))</f>
+        <v>773400</v>
+      </c>
+      <c r="F14" s="40" t="str">
+        <f aca="false">IF(E14="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A14,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A14,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G14" s="41" t="str">
+        <f aca="false">IF(AND(C14="平日",E14&lt;&gt;""),E14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="n">
+        <f aca="false">IF(AND(C14="土日",E14&lt;&gt;""),E14,"")</f>
+        <v>773400</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B15" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A15),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C15" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A15)=1,WEEKDAY(A15)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A15,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A15,土日!$A$2:$A$28,0)),""))</f>
+        <v>786550</v>
+      </c>
+      <c r="F15" s="40" t="str">
+        <f aca="false">IF(E15="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A15,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A15,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G15" s="41" t="str">
+        <f aca="false">IF(AND(C15="平日",E15&lt;&gt;""),E15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="41" t="n">
+        <f aca="false">IF(AND(C15="土日",E15&lt;&gt;""),E15,"")</f>
+        <v>786550</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B16" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A16),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C16" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A16)=1,WEEKDAY(A16)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A16,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A16,土日!$A$2:$A$28,0)),""))</f>
+        <v>372650</v>
+      </c>
+      <c r="F16" s="5" t="str">
+        <f aca="false">IF(E16="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A16,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A16,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <f aca="false">IF(AND(C16="平日",E16&lt;&gt;""),E16,"")</f>
+        <v>372650</v>
+      </c>
+      <c r="H16" s="7" t="str">
+        <f aca="false">IF(AND(C16="土日",E16&lt;&gt;""),E16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B17" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A17),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C17" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A17)=1,WEEKDAY(A17)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A17,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A17,土日!$A$2:$A$28,0)),""))</f>
+        <v>289840</v>
+      </c>
+      <c r="F17" s="5" t="str">
+        <f aca="false">IF(E17="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A17,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A17,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <f aca="false">IF(AND(C17="平日",E17&lt;&gt;""),E17,"")</f>
+        <v>289840</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <f aca="false">IF(AND(C17="土日",E17&lt;&gt;""),E17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B18" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A18),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C18" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A18)=1,WEEKDAY(A18)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A18,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A18,土日!$A$2:$A$28,0)),""))</f>
+        <v>418780</v>
+      </c>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(E18="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A18,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A18,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <f aca="false">IF(AND(C18="平日",E18&lt;&gt;""),E18,"")</f>
+        <v>418780</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <f aca="false">IF(AND(C18="土日",E18&lt;&gt;""),E18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B19" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A19),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C19" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A19)=1,WEEKDAY(A19)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A19,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A19,土日!$A$2:$A$28,0)),""))</f>
+        <v>459900</v>
+      </c>
+      <c r="F19" s="5" t="str">
+        <f aca="false">IF(E19="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A19,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A19,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <f aca="false">IF(AND(C19="平日",E19&lt;&gt;""),E19,"")</f>
+        <v>459900</v>
+      </c>
+      <c r="H19" s="7" t="str">
+        <f aca="false">IF(AND(C19="土日",E19&lt;&gt;""),E19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B20" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A20),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C20" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A20)=1,WEEKDAY(A20)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A20,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A20,土日!$A$2:$A$28,0)),""))</f>
+        <v>493180</v>
+      </c>
+      <c r="F20" s="5" t="str">
+        <f aca="false">IF(E20="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A20,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A20,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <f aca="false">IF(AND(C20="平日",E20&lt;&gt;""),E20,"")</f>
+        <v>493180</v>
+      </c>
+      <c r="H20" s="7" t="str">
+        <f aca="false">IF(AND(C20="土日",E20&lt;&gt;""),E20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="38" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B21" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A21),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C21" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A21)=1,WEEKDAY(A21)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A21,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A21,土日!$A$2:$A$28,0)),""))</f>
+        <v>652640</v>
+      </c>
+      <c r="F21" s="40" t="str">
+        <f aca="false">IF(E21="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A21,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A21,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G21" s="41" t="str">
+        <f aca="false">IF(AND(C21="平日",E21&lt;&gt;""),E21,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="41" t="n">
+        <f aca="false">IF(AND(C21="土日",E21&lt;&gt;""),E21,"")</f>
+        <v>652640</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="38" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B22" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A22),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C22" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A22)=1,WEEKDAY(A22)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D22" s="40"/>
+      <c r="E22" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A22,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A22,土日!$A$2:$A$28,0)),""))</f>
+        <v>737850</v>
+      </c>
+      <c r="F22" s="40" t="str">
+        <f aca="false">IF(E22="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A22,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A22,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G22" s="41" t="str">
+        <f aca="false">IF(AND(C22="平日",E22&lt;&gt;""),E22,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="41" t="n">
+        <f aca="false">IF(AND(C22="土日",E22&lt;&gt;""),E22,"")</f>
+        <v>737850</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="33" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B23" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A23),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C23" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A23)=1,WEEKDAY(A23)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A23,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A23,土日!$A$2:$A$28,0)),""))</f>
+        <v>597070</v>
+      </c>
+      <c r="F23" s="5" t="str">
+        <f aca="false">IF(E23="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A23,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A23,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <f aca="false">IF(AND(C23="平日",E23&lt;&gt;""),E23,"")</f>
+        <v>597070</v>
+      </c>
+      <c r="H23" s="7" t="str">
+        <f aca="false">IF(AND(C23="土日",E23&lt;&gt;""),E23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B24" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A24),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C24" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A24)=1,WEEKDAY(A24)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A24,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A24,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F24" s="45" t="str">
+        <f aca="false">IF(E24="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A24,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A24,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G24" s="7" t="str">
+        <f aca="false">IF(AND(C24="平日",E24&lt;&gt;""),E24,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="7" t="str">
+        <f aca="false">IF(AND(C24="土日",E24&lt;&gt;""),E24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="33" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B25" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A25),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C25" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A25)=1,WEEKDAY(A25)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A25,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A25,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" s="45" t="str">
+        <f aca="false">IF(E25="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A25,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A25,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G25" s="7" t="str">
+        <f aca="false">IF(AND(C25="平日",E25&lt;&gt;""),E25,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="7" t="str">
+        <f aca="false">IF(AND(C25="土日",E25&lt;&gt;""),E25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B26" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A26),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C26" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A26)=1,WEEKDAY(A26)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A26,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A26,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F26" s="45" t="str">
+        <f aca="false">IF(E26="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A26,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A26,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G26" s="7" t="str">
+        <f aca="false">IF(AND(C26="平日",E26&lt;&gt;""),E26,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="7" t="str">
+        <f aca="false">IF(AND(C26="土日",E26&lt;&gt;""),E26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B27" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A27),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C27" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A27)=1,WEEKDAY(A27)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A27,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A27,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F27" s="45" t="str">
+        <f aca="false">IF(E27="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A27,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A27,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G27" s="7" t="str">
+        <f aca="false">IF(AND(C27="平日",E27&lt;&gt;""),E27,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="7" t="str">
+        <f aca="false">IF(AND(C27="土日",E27&lt;&gt;""),E27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="38" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B28" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A28),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C28" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A28)=1,WEEKDAY(A28)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D28" s="40"/>
+      <c r="E28" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A28,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A28,土日!$A$2:$A$28,0)),""))</f>
+        <v>615300</v>
+      </c>
+      <c r="F28" s="40" t="str">
+        <f aca="false">IF(E28="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A28,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A28,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G28" s="41" t="str">
+        <f aca="false">IF(AND(C28="平日",E28&lt;&gt;""),E28,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="41" t="n">
+        <f aca="false">IF(AND(C28="土日",E28&lt;&gt;""),E28,"")</f>
+        <v>615300</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="38" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B29" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A29),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C29" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A29)=1,WEEKDAY(A29)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D29" s="40"/>
+      <c r="E29" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A29,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A29,土日!$A$2:$A$28,0)),""))</f>
+        <v>695890</v>
+      </c>
+      <c r="F29" s="40" t="str">
+        <f aca="false">IF(E29="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A29,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A29,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G29" s="41" t="str">
+        <f aca="false">IF(AND(C29="平日",E29&lt;&gt;""),E29,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="41" t="n">
+        <f aca="false">IF(AND(C29="土日",E29&lt;&gt;""),E29,"")</f>
+        <v>695890</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B30" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A30),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C30" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A30)=1,WEEKDAY(A30)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A30,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A30,土日!$A$2:$A$28,0)),""))</f>
+        <v>395610</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f aca="false">IF(E30="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A30,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A30,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <f aca="false">IF(AND(C30="平日",E30&lt;&gt;""),E30,"")</f>
+        <v>395610</v>
+      </c>
+      <c r="H30" s="7" t="str">
+        <f aca="false">IF(AND(C30="土日",E30&lt;&gt;""),E30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B31" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A31),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C31" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A31)=1,WEEKDAY(A31)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A31,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A31,土日!$A$2:$A$28,0)),""))</f>
+        <v>357540</v>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f aca="false">IF(E31="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A31,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A31,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <f aca="false">IF(AND(C31="平日",E31&lt;&gt;""),E31,"")</f>
+        <v>357540</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <f aca="false">IF(AND(C31="土日",E31&lt;&gt;""),E31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B32" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A32),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C32" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A32)=1,WEEKDAY(A32)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A32,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A32,土日!$A$2:$A$28,0)),""))</f>
+        <v>383270</v>
+      </c>
+      <c r="F32" s="5" t="str">
+        <f aca="false">IF(E32="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A32,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A32,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <f aca="false">IF(AND(C32="平日",E32&lt;&gt;""),E32,"")</f>
+        <v>383270</v>
+      </c>
+      <c r="H32" s="7" t="str">
+        <f aca="false">IF(AND(C32="土日",E32&lt;&gt;""),E32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B33" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A33),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C33" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A33)=1,WEEKDAY(A33)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A33,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A33,土日!$A$2:$A$28,0)),""))</f>
+        <v>397380</v>
+      </c>
+      <c r="F33" s="5" t="str">
+        <f aca="false">IF(E33="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A33,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A33,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <f aca="false">IF(AND(C33="平日",E33&lt;&gt;""),E33,"")</f>
+        <v>397380</v>
+      </c>
+      <c r="H33" s="7" t="str">
+        <f aca="false">IF(AND(C33="土日",E33&lt;&gt;""),E33,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B34" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A34),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C34" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A34)=1,WEEKDAY(A34)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A34,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A34,土日!$A$2:$A$28,0)),""))</f>
+        <v>533650</v>
+      </c>
+      <c r="F34" s="5" t="str">
+        <f aca="false">IF(E34="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A34,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A34,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <f aca="false">IF(AND(C34="平日",E34&lt;&gt;""),E34,"")</f>
+        <v>533650</v>
+      </c>
+      <c r="H34" s="7" t="str">
+        <f aca="false">IF(AND(C34="土日",E34&lt;&gt;""),E34,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="38" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B4" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A4),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C4" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A4)=1,WEEKDAY(A4)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A4,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A4,土日!$A$2:$A$28,0)),""))</f>
+        <v>664790</v>
+      </c>
+      <c r="F4" s="40" t="str">
+        <f aca="false">IF(E4="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A4,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A4,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G4" s="41" t="str">
+        <f aca="false">IF(AND(C4="平日",E4&lt;&gt;""),E4,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="41" t="n">
+        <f aca="false">IF(AND(C4="土日",E4&lt;&gt;""),E4,"")</f>
+        <v>664790</v>
+      </c>
+      <c r="J4" s="35"/>
+      <c r="K4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="38" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B5" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A5),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C5" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A5)=1,WEEKDAY(A5)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D5" s="40"/>
+      <c r="E5" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A5,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A5,土日!$A$2:$A$28,0)),""))</f>
+        <v>711580</v>
+      </c>
+      <c r="F5" s="40" t="str">
+        <f aca="false">IF(E5="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A5,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A5,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G5" s="41" t="str">
+        <f aca="false">IF(AND(C5="平日",E5&lt;&gt;""),E5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="41" t="n">
+        <f aca="false">IF(AND(C5="土日",E5&lt;&gt;""),E5,"")</f>
+        <v>711580</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <f aca="false">SUM(G4:G34)</f>
+        <v>3704280</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <f aca="false">SUM(H4:H34)</f>
+        <v>2408450</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <f aca="false">K5+L5</f>
+        <v>6112730</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B6" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A6),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C6" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A6)=1,WEEKDAY(A6)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A6,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A6,土日!$A$2:$A$28,0)),""))</f>
+        <v>363910</v>
+      </c>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(E6="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A6,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A6,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <f aca="false">IF(AND(C6="平日",E6&lt;&gt;""),E6,"")</f>
+        <v>363910</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f aca="false">IF(AND(C6="土日",E6&lt;&gt;""),E6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <f aca="false">COUNT(G4:G34)</f>
+        <v>11</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <f aca="false">COUNT(H4:H34)</f>
+        <v>4</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <f aca="false">K6+L6</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B7" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A7),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C7" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A7)=1,WEEKDAY(A7)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A7,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A7,土日!$A$2:$A$28,0)),""))</f>
+        <v>360990</v>
+      </c>
+      <c r="F7" s="5" t="str">
+        <f aca="false">IF(E7="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A7,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A7,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <f aca="false">IF(AND(C7="平日",E7&lt;&gt;""),E7,"")</f>
+        <v>360990</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f aca="false">IF(AND(C7="土日",E7&lt;&gt;""),E7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <f aca="false">IF(K6=0,0,K5/K6)</f>
+        <v>336752.727272727</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <f aca="false">IF(L6=0,0,L5/L6)</f>
+        <v>602112.5</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <f aca="false">IF(M6=0,0,M5/M6)</f>
+        <v>407515.333333333</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B8" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A8),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C8" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A8)=1,WEEKDAY(A8)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A8,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A8,土日!$A$2:$A$28,0)),""))</f>
+        <v>383160</v>
+      </c>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(E8="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A8,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A8,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <f aca="false">IF(AND(C8="平日",E8&lt;&gt;""),E8,"")</f>
+        <v>383160</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f aca="false">IF(AND(C8="土日",E8&lt;&gt;""),E8,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <f aca="false">MAX(G4:G34)</f>
+        <v>449020</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <f aca="false">MAX(H4:H34)</f>
+        <v>711580</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <f aca="false">MAX(K8:L8)</f>
+        <v>711580</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B9" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A9),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C9" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A9)=1,WEEKDAY(A9)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A9,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A9,土日!$A$2:$A$28,0)),""))</f>
+        <v>388830</v>
+      </c>
+      <c r="F9" s="5" t="str">
+        <f aca="false">IF(E9="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A9,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A9,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <f aca="false">IF(AND(C9="平日",E9&lt;&gt;""),E9,"")</f>
+        <v>388830</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f aca="false">IF(AND(C9="土日",E9&lt;&gt;""),E9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <f aca="false">MIN(G4:G34)</f>
+        <v>219670</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <f aca="false">MIN(H4:H34)</f>
+        <v>477270</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <f aca="false">MIN(K9:L9)</f>
+        <v>219670</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B10" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A10),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C10" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A10)=1,WEEKDAY(A10)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A10,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A10,土日!$A$2:$A$28,0)),""))</f>
+        <v>449020</v>
+      </c>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(E10="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A10,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A10,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <f aca="false">IF(AND(C10="平日",E10&lt;&gt;""),E10,"")</f>
+        <v>449020</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f aca="false">IF(AND(C10="土日",E10&lt;&gt;""),E10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,K5/M5)</f>
+        <v>0.605994375671754</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,L5/M5)</f>
+        <v>0.394005624328246</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <f aca="false">K10+L10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="38" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B11" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A11),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C11" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A11)=1,WEEKDAY(A11)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A11,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A11,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F11" s="46" t="str">
+        <f aca="false">IF(E11="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A11,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A11,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G11" s="41" t="str">
+        <f aca="false">IF(AND(C11="平日",E11&lt;&gt;""),E11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="41" t="str">
+        <f aca="false">IF(AND(C11="土日",E11&lt;&gt;""),E11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <f aca="false">IF(K7=0,0,L7/K7)</f>
+        <v>1.78799591283596</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="38" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B12" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A12),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C12" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A12)=1,WEEKDAY(A12)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A12,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A12,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F12" s="46" t="str">
+        <f aca="false">IF(E12="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A12,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A12,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G12" s="41" t="str">
+        <f aca="false">IF(AND(C12="平日",E12&lt;&gt;""),E12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="41" t="str">
+        <f aca="false">IF(AND(C12="土日",E12&lt;&gt;""),E12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="43" t="n">
+        <f aca="false">COUNTIF(F4:F34,"報告なし")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B13" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A13),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C13" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A13)=1,WEEKDAY(A13)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A13,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A13,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F13" s="45" t="str">
+        <f aca="false">IF(E13="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A13,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A13,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G13" s="7" t="str">
+        <f aca="false">IF(AND(C13="平日",E13&lt;&gt;""),E13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="7" t="str">
+        <f aca="false">IF(AND(C13="土日",E13&lt;&gt;""),E13,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A14),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C14" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A14)=1,WEEKDAY(A14)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A14,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A14,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F14" s="45" t="str">
+        <f aca="false">IF(E14="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A14,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A14,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G14" s="7" t="str">
+        <f aca="false">IF(AND(C14="平日",E14&lt;&gt;""),E14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="7" t="str">
+        <f aca="false">IF(AND(C14="土日",E14&lt;&gt;""),E14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B15" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A15),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C15" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A15)=1,WEEKDAY(A15)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A15,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A15,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F15" s="45" t="str">
+        <f aca="false">IF(E15="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A15,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A15,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <f aca="false">IF(AND(C15="平日",E15&lt;&gt;""),E15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="7" t="str">
+        <f aca="false">IF(AND(C15="土日",E15&lt;&gt;""),E15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B16" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A16),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C16" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A16)=1,WEEKDAY(A16)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A16,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A16,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F16" s="45" t="str">
+        <f aca="false">IF(E16="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A16,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A16,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G16" s="7" t="str">
+        <f aca="false">IF(AND(C16="平日",E16&lt;&gt;""),E16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="7" t="str">
+        <f aca="false">IF(AND(C16="土日",E16&lt;&gt;""),E16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B17" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A17),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C17" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A17)=1,WEEKDAY(A17)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A17,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A17,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F17" s="45" t="str">
+        <f aca="false">IF(E17="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A17,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A17,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <f aca="false">IF(AND(C17="平日",E17&lt;&gt;""),E17,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="7" t="str">
+        <f aca="false">IF(AND(C17="土日",E17&lt;&gt;""),E17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="38" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B18" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A18),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C18" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A18)=1,WEEKDAY(A18)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A18,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A18,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F18" s="46" t="str">
+        <f aca="false">IF(E18="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A18,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A18,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G18" s="41" t="str">
+        <f aca="false">IF(AND(C18="平日",E18&lt;&gt;""),E18,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="41" t="str">
+        <f aca="false">IF(AND(C18="土日",E18&lt;&gt;""),E18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="38" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B19" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A19),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C19" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A19)=1,WEEKDAY(A19)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A19,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A19,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F19" s="46" t="str">
+        <f aca="false">IF(E19="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A19,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A19,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G19" s="41" t="str">
+        <f aca="false">IF(AND(C19="平日",E19&lt;&gt;""),E19,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="41" t="str">
+        <f aca="false">IF(AND(C19="土日",E19&lt;&gt;""),E19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B20" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A20),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C20" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A20)=1,WEEKDAY(A20)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A20,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A20,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F20" s="45" t="str">
+        <f aca="false">IF(E20="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A20,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A20,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G20" s="7" t="str">
+        <f aca="false">IF(AND(C20="平日",E20&lt;&gt;""),E20,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="7" t="str">
+        <f aca="false">IF(AND(C20="土日",E20&lt;&gt;""),E20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="33" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B21" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A21),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C21" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A21)=1,WEEKDAY(A21)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A21,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A21,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F21" s="45" t="str">
+        <f aca="false">IF(E21="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A21,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A21,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G21" s="7" t="str">
+        <f aca="false">IF(AND(C21="平日",E21&lt;&gt;""),E21,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="7" t="str">
+        <f aca="false">IF(AND(C21="土日",E21&lt;&gt;""),E21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B22" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A22),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C22" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A22)=1,WEEKDAY(A22)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A22,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A22,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F22" s="45" t="str">
+        <f aca="false">IF(E22="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A22,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A22,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G22" s="7" t="str">
+        <f aca="false">IF(AND(C22="平日",E22&lt;&gt;""),E22,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="7" t="str">
+        <f aca="false">IF(AND(C22="土日",E22&lt;&gt;""),E22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B23" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A23),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C23" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A23)=1,WEEKDAY(A23)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A23,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A23,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F23" s="45" t="str">
+        <f aca="false">IF(E23="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A23,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A23,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G23" s="7" t="str">
+        <f aca="false">IF(AND(C23="平日",E23&lt;&gt;""),E23,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="7" t="str">
+        <f aca="false">IF(AND(C23="土日",E23&lt;&gt;""),E23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B24" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A24),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C24" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A24)=1,WEEKDAY(A24)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A24,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A24,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F24" s="45" t="str">
+        <f aca="false">IF(E24="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A24,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A24,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G24" s="7" t="str">
+        <f aca="false">IF(AND(C24="平日",E24&lt;&gt;""),E24,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="7" t="str">
+        <f aca="false">IF(AND(C24="土日",E24&lt;&gt;""),E24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="38" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B25" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A25),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C25" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A25)=1,WEEKDAY(A25)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D25" s="40"/>
+      <c r="E25" s="41" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A25,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A25,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" s="46" t="str">
+        <f aca="false">IF(E25="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A25,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A25,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G25" s="41" t="str">
+        <f aca="false">IF(AND(C25="平日",E25&lt;&gt;""),E25,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="41" t="str">
+        <f aca="false">IF(AND(C25="土日",E25&lt;&gt;""),E25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="38" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B26" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A26),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C26" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A26)=1,WEEKDAY(A26)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D26" s="40"/>
+      <c r="E26" s="41" t="str">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A26,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A26,土日!$A$2:$A$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F26" s="46" t="str">
+        <f aca="false">IF(E26="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A26,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A26,土日!$A$2:$A$28,0))))</f>
+        <v>報告なし</v>
+      </c>
+      <c r="G26" s="41" t="str">
+        <f aca="false">IF(AND(C26="平日",E26&lt;&gt;""),E26,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="41" t="str">
+        <f aca="false">IF(AND(C26="土日",E26&lt;&gt;""),E26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B27" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A27),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C27" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A27)=1,WEEKDAY(A27)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A27,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A27,土日!$A$2:$A$28,0)),""))</f>
+        <v>268730</v>
+      </c>
+      <c r="F27" s="5" t="str">
+        <f aca="false">IF(E27="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A27,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A27,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <f aca="false">IF(AND(C27="平日",E27&lt;&gt;""),E27,"")</f>
+        <v>268730</v>
+      </c>
+      <c r="H27" s="7" t="str">
+        <f aca="false">IF(AND(C27="土日",E27&lt;&gt;""),E27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B28" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A28),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C28" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A28)=1,WEEKDAY(A28)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A28,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A28,土日!$A$2:$A$28,0)),""))</f>
+        <v>256280</v>
+      </c>
+      <c r="F28" s="5" t="str">
+        <f aca="false">IF(E28="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A28,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A28,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <f aca="false">IF(AND(C28="平日",E28&lt;&gt;""),E28,"")</f>
+        <v>256280</v>
+      </c>
+      <c r="H28" s="7" t="str">
+        <f aca="false">IF(AND(C28="土日",E28&lt;&gt;""),E28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="33" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B29" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A29),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C29" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A29)=1,WEEKDAY(A29)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A29,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A29,土日!$A$2:$A$28,0)),""))</f>
+        <v>351140</v>
+      </c>
+      <c r="F29" s="5" t="str">
+        <f aca="false">IF(E29="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A29,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A29,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <f aca="false">IF(AND(C29="平日",E29&lt;&gt;""),E29,"")</f>
+        <v>351140</v>
+      </c>
+      <c r="H29" s="7" t="str">
+        <f aca="false">IF(AND(C29="土日",E29&lt;&gt;""),E29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B30" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A30),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C30" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A30)=1,WEEKDAY(A30)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A30,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A30,土日!$A$2:$A$28,0)),""))</f>
+        <v>299580</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f aca="false">IF(E30="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A30,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A30,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <f aca="false">IF(AND(C30="平日",E30&lt;&gt;""),E30,"")</f>
+        <v>299580</v>
+      </c>
+      <c r="H30" s="7" t="str">
+        <f aca="false">IF(AND(C30="土日",E30&lt;&gt;""),E30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B31" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A31),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C31" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A31)=1,WEEKDAY(A31)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A31,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A31,土日!$A$2:$A$28,0)),""))</f>
+        <v>362970</v>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f aca="false">IF(E31="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A31,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A31,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <f aca="false">IF(AND(C31="平日",E31&lt;&gt;""),E31,"")</f>
+        <v>362970</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <f aca="false">IF(AND(C31="土日",E31&lt;&gt;""),E31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="38" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B32" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A32),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C32" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A32)=1,WEEKDAY(A32)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D32" s="40"/>
+      <c r="E32" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A32,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A32,土日!$A$2:$A$28,0)),""))</f>
+        <v>554810</v>
+      </c>
+      <c r="F32" s="40" t="str">
+        <f aca="false">IF(E32="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A32,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A32,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G32" s="41" t="str">
+        <f aca="false">IF(AND(C32="平日",E32&lt;&gt;""),E32,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="41" t="n">
+        <f aca="false">IF(AND(C32="土日",E32&lt;&gt;""),E32,"")</f>
+        <v>554810</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="38" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B33" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A33),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C33" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A33)=1,WEEKDAY(A33)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A33,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A33,土日!$A$2:$A$28,0)),""))</f>
+        <v>477270</v>
+      </c>
+      <c r="F33" s="40" t="str">
+        <f aca="false">IF(E33="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A33,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A33,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G33" s="41" t="str">
+        <f aca="false">IF(AND(C33="平日",E33&lt;&gt;""),E33,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="41" t="n">
+        <f aca="false">IF(AND(C33="土日",E33&lt;&gt;""),E33,"")</f>
+        <v>477270</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B34" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A34),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C34" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A34)=1,WEEKDAY(A34)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A34,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A34,土日!$A$2:$A$28,0)),""))</f>
+        <v>219670</v>
+      </c>
+      <c r="F34" s="5" t="str">
+        <f aca="false">IF(E34="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A34,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A34,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <f aca="false">IF(AND(C34="平日",E34&lt;&gt;""),E34,"")</f>
+        <v>219670</v>
+      </c>
+      <c r="H34" s="7" t="str">
+        <f aca="false">IF(AND(C34="土日",E34&lt;&gt;""),E34,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A4),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C4" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A4)=1,WEEKDAY(A4)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A4,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A4,土日!$A$2:$A$28,0)),""))</f>
+        <v>228460</v>
+      </c>
+      <c r="F4" s="5" t="str">
+        <f aca="false">IF(E4="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A4,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A4,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <f aca="false">IF(AND(C4="平日",E4&lt;&gt;""),E4,"")</f>
+        <v>228460</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f aca="false">IF(AND(C4="土日",E4&lt;&gt;""),E4,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="35"/>
+      <c r="K4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A5),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C5" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A5)=1,WEEKDAY(A5)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A5,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A5,土日!$A$2:$A$28,0)),""))</f>
+        <v>214940</v>
+      </c>
+      <c r="F5" s="5" t="str">
+        <f aca="false">IF(E5="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A5,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A5,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <f aca="false">IF(AND(C5="平日",E5&lt;&gt;""),E5,"")</f>
+        <v>214940</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f aca="false">IF(AND(C5="土日",E5&lt;&gt;""),E5,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <f aca="false">SUM(G4:G33)</f>
+        <v>6149490</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <f aca="false">SUM(H4:H33)</f>
+        <v>4303390</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <f aca="false">K5+L5</f>
+        <v>10452880</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A6),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C6" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A6)=1,WEEKDAY(A6)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A6,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A6,土日!$A$2:$A$28,0)),""))</f>
+        <v>263030</v>
+      </c>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(E6="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A6,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A6,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <f aca="false">IF(AND(C6="平日",E6&lt;&gt;""),E6,"")</f>
+        <v>263030</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f aca="false">IF(AND(C6="土日",E6&lt;&gt;""),E6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <f aca="false">COUNT(G4:G33)</f>
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <f aca="false">COUNT(H4:H33)</f>
+        <v>8</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <f aca="false">K6+L6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B7" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A7),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C7" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A7)=1,WEEKDAY(A7)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A7,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A7,土日!$A$2:$A$28,0)),""))</f>
+        <v>212930</v>
+      </c>
+      <c r="F7" s="5" t="str">
+        <f aca="false">IF(E7="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A7,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A7,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <f aca="false">IF(AND(C7="平日",E7&lt;&gt;""),E7,"")</f>
+        <v>212930</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f aca="false">IF(AND(C7="土日",E7&lt;&gt;""),E7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <f aca="false">IF(K6=0,0,K5/K6)</f>
+        <v>279522.272727273</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <f aca="false">IF(L6=0,0,L5/L6)</f>
+        <v>537923.75</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <f aca="false">IF(M6=0,0,M5/M6)</f>
+        <v>348429.333333333</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="38" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B8" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A8),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C8" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A8)=1,WEEKDAY(A8)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A8,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A8,土日!$A$2:$A$28,0)),""))</f>
+        <v>573870</v>
+      </c>
+      <c r="F8" s="40" t="str">
+        <f aca="false">IF(E8="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A8,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A8,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G8" s="41" t="str">
+        <f aca="false">IF(AND(C8="平日",E8&lt;&gt;""),E8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="41" t="n">
+        <f aca="false">IF(AND(C8="土日",E8&lt;&gt;""),E8,"")</f>
+        <v>573870</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <f aca="false">MAX(G4:G33)</f>
+        <v>606440</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <f aca="false">MAX(H4:H33)</f>
+        <v>586850</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <f aca="false">MAX(K8:L8)</f>
+        <v>606440</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="38" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B9" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A9),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C9" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A9)=1,WEEKDAY(A9)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A9,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A9,土日!$A$2:$A$28,0)),""))</f>
+        <v>543590</v>
+      </c>
+      <c r="F9" s="40" t="str">
+        <f aca="false">IF(E9="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A9,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A9,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G9" s="41" t="str">
+        <f aca="false">IF(AND(C9="平日",E9&lt;&gt;""),E9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="41" t="n">
+        <f aca="false">IF(AND(C9="土日",E9&lt;&gt;""),E9,"")</f>
+        <v>543590</v>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <f aca="false">MIN(G4:G33)</f>
+        <v>167060</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <f aca="false">MIN(H4:H33)</f>
+        <v>466800</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <f aca="false">MIN(K9:L9)</f>
+        <v>167060</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A10),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C10" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A10)=1,WEEKDAY(A10)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A10,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A10,土日!$A$2:$A$28,0)),""))</f>
+        <v>207730</v>
+      </c>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(E10="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A10,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A10,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <f aca="false">IF(AND(C10="平日",E10&lt;&gt;""),E10,"")</f>
+        <v>207730</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f aca="false">IF(AND(C10="土日",E10&lt;&gt;""),E10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,K5/M5)</f>
+        <v>0.588305806629369</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <f aca="false">IF(M5=0,0,L5/M5)</f>
+        <v>0.411694193370631</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <f aca="false">K10+L10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B11" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A11),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C11" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A11)=1,WEEKDAY(A11)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A11,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A11,土日!$A$2:$A$28,0)),""))</f>
+        <v>335170</v>
+      </c>
+      <c r="F11" s="5" t="str">
+        <f aca="false">IF(E11="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A11,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A11,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <f aca="false">IF(AND(C11="平日",E11&lt;&gt;""),E11,"")</f>
+        <v>335170</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <f aca="false">IF(AND(C11="土日",E11&lt;&gt;""),E11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <f aca="false">IF(K7=0,0,L7/K7)</f>
+        <v>1.92443966898068</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B12" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A12),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C12" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A12)=1,WEEKDAY(A12)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A12,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A12,土日!$A$2:$A$28,0)),""))</f>
+        <v>212760</v>
+      </c>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(E12="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A12,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A12,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <f aca="false">IF(AND(C12="平日",E12&lt;&gt;""),E12,"")</f>
+        <v>212760</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f aca="false">IF(AND(C12="土日",E12&lt;&gt;""),E12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="43" t="n">
+        <f aca="false">COUNTIF(F4:F33,"報告なし")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B13" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A13),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C13" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A13)=1,WEEKDAY(A13)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A13,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A13,土日!$A$2:$A$28,0)),""))</f>
+        <v>294500</v>
+      </c>
+      <c r="F13" s="5" t="str">
+        <f aca="false">IF(E13="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A13,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A13,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <f aca="false">IF(AND(C13="平日",E13&lt;&gt;""),E13,"")</f>
+        <v>294500</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <f aca="false">IF(AND(C13="土日",E13&lt;&gt;""),E13,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B14" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A14),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C14" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A14)=1,WEEKDAY(A14)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A14,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A14,土日!$A$2:$A$28,0)),""))</f>
+        <v>320850</v>
+      </c>
+      <c r="F14" s="5" t="str">
+        <f aca="false">IF(E14="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A14,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A14,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <f aca="false">IF(AND(C14="平日",E14&lt;&gt;""),E14,"")</f>
+        <v>320850</v>
+      </c>
+      <c r="H14" s="7" t="str">
+        <f aca="false">IF(AND(C14="土日",E14&lt;&gt;""),E14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B15" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A15),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C15" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A15)=1,WEEKDAY(A15)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A15,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A15,土日!$A$2:$A$28,0)),""))</f>
+        <v>507490</v>
+      </c>
+      <c r="F15" s="40" t="str">
+        <f aca="false">IF(E15="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A15,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A15,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G15" s="41" t="str">
+        <f aca="false">IF(AND(C15="平日",E15&lt;&gt;""),E15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="41" t="n">
+        <f aca="false">IF(AND(C15="土日",E15&lt;&gt;""),E15,"")</f>
+        <v>507490</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B16" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A16),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C16" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A16)=1,WEEKDAY(A16)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A16,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A16,土日!$A$2:$A$28,0)),""))</f>
+        <v>543290</v>
+      </c>
+      <c r="F16" s="40" t="str">
+        <f aca="false">IF(E16="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A16,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A16,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G16" s="41" t="str">
+        <f aca="false">IF(AND(C16="平日",E16&lt;&gt;""),E16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="41" t="n">
+        <f aca="false">IF(AND(C16="土日",E16&lt;&gt;""),E16,"")</f>
+        <v>543290</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B17" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A17),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C17" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A17)=1,WEEKDAY(A17)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A17,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A17,土日!$A$2:$A$28,0)),""))</f>
+        <v>215510</v>
+      </c>
+      <c r="F17" s="5" t="str">
+        <f aca="false">IF(E17="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A17,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A17,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <f aca="false">IF(AND(C17="平日",E17&lt;&gt;""),E17,"")</f>
+        <v>215510</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <f aca="false">IF(AND(C17="土日",E17&lt;&gt;""),E17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B18" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A18),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C18" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A18)=1,WEEKDAY(A18)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A18,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A18,土日!$A$2:$A$28,0)),""))</f>
+        <v>167060</v>
+      </c>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(E18="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A18,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A18,土日!$A$2:$A$28,0))))</f>
+        <v>かりん</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <f aca="false">IF(AND(C18="平日",E18&lt;&gt;""),E18,"")</f>
+        <v>167060</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <f aca="false">IF(AND(C18="土日",E18&lt;&gt;""),E18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B19" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A19),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C19" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A19)=1,WEEKDAY(A19)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A19,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A19,土日!$A$2:$A$28,0)),""))</f>
+        <v>392050</v>
+      </c>
+      <c r="F19" s="5" t="str">
+        <f aca="false">IF(E19="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A19,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A19,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <f aca="false">IF(AND(C19="平日",E19&lt;&gt;""),E19,"")</f>
+        <v>392050</v>
+      </c>
+      <c r="H19" s="7" t="str">
+        <f aca="false">IF(AND(C19="土日",E19&lt;&gt;""),E19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B20" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A20),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C20" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A20)=1,WEEKDAY(A20)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A20,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A20,土日!$A$2:$A$28,0)),""))</f>
+        <v>259100</v>
+      </c>
+      <c r="F20" s="5" t="str">
+        <f aca="false">IF(E20="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A20,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A20,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <f aca="false">IF(AND(C20="平日",E20&lt;&gt;""),E20,"")</f>
+        <v>259100</v>
+      </c>
+      <c r="H20" s="7" t="str">
+        <f aca="false">IF(AND(C20="土日",E20&lt;&gt;""),E20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="33" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B21" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A21),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C21" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A21)=1,WEEKDAY(A21)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A21,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A21,土日!$A$2:$A$28,0)),""))</f>
+        <v>278990</v>
+      </c>
+      <c r="F21" s="5" t="str">
+        <f aca="false">IF(E21="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A21,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A21,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <f aca="false">IF(AND(C21="平日",E21&lt;&gt;""),E21,"")</f>
+        <v>278990</v>
+      </c>
+      <c r="H21" s="7" t="str">
+        <f aca="false">IF(AND(C21="土日",E21&lt;&gt;""),E21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="38" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B22" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A22),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C22" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A22)=1,WEEKDAY(A22)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D22" s="40"/>
+      <c r="E22" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A22,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A22,土日!$A$2:$A$28,0)),""))</f>
+        <v>466800</v>
+      </c>
+      <c r="F22" s="40" t="str">
+        <f aca="false">IF(E22="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A22,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A22,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G22" s="41" t="str">
+        <f aca="false">IF(AND(C22="平日",E22&lt;&gt;""),E22,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="41" t="n">
+        <f aca="false">IF(AND(C22="土日",E22&lt;&gt;""),E22,"")</f>
+        <v>466800</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="38" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B23" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A23),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C23" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A23)=1,WEEKDAY(A23)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D23" s="40"/>
+      <c r="E23" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A23,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A23,土日!$A$2:$A$28,0)),""))</f>
+        <v>586850</v>
+      </c>
+      <c r="F23" s="40" t="str">
+        <f aca="false">IF(E23="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A23,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A23,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G23" s="41" t="str">
+        <f aca="false">IF(AND(C23="平日",E23&lt;&gt;""),E23,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="41" t="n">
+        <f aca="false">IF(AND(C23="土日",E23&lt;&gt;""),E23,"")</f>
+        <v>586850</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B24" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A24),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C24" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A24)=1,WEEKDAY(A24)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A24,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A24,土日!$A$2:$A$28,0)),""))</f>
+        <v>606440</v>
+      </c>
+      <c r="F24" s="5" t="str">
+        <f aca="false">IF(E24="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A24,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A24,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <f aca="false">IF(AND(C24="平日",E24&lt;&gt;""),E24,"")</f>
+        <v>606440</v>
+      </c>
+      <c r="H24" s="7" t="str">
+        <f aca="false">IF(AND(C24="土日",E24&lt;&gt;""),E24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B25" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A25),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C25" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A25)=1,WEEKDAY(A25)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A25,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A25,土日!$A$2:$A$28,0)),""))</f>
+        <v>471650</v>
+      </c>
+      <c r="F25" s="5" t="str">
+        <f aca="false">IF(E25="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A25,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A25,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <f aca="false">IF(AND(C25="平日",E25&lt;&gt;""),E25,"")</f>
+        <v>471650</v>
+      </c>
+      <c r="H25" s="7" t="str">
+        <f aca="false">IF(AND(C25="土日",E25&lt;&gt;""),E25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B26" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A26),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C26" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A26)=1,WEEKDAY(A26)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A26,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A26,土日!$A$2:$A$28,0)),""))</f>
+        <v>425490</v>
+      </c>
+      <c r="F26" s="5" t="str">
+        <f aca="false">IF(E26="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A26,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A26,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <f aca="false">IF(AND(C26="平日",E26&lt;&gt;""),E26,"")</f>
+        <v>425490</v>
+      </c>
+      <c r="H26" s="7" t="str">
+        <f aca="false">IF(AND(C26="土日",E26&lt;&gt;""),E26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B27" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A27),1)</f>
+        <v>木</v>
+      </c>
+      <c r="C27" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A27)=1,WEEKDAY(A27)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A27,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A27,土日!$A$2:$A$28,0)),""))</f>
+        <v>223490</v>
+      </c>
+      <c r="F27" s="5" t="str">
+        <f aca="false">IF(E27="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A27,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A27,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <f aca="false">IF(AND(C27="平日",E27&lt;&gt;""),E27,"")</f>
+        <v>223490</v>
+      </c>
+      <c r="H27" s="7" t="str">
+        <f aca="false">IF(AND(C27="土日",E27&lt;&gt;""),E27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B28" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A28),1)</f>
+        <v>金</v>
+      </c>
+      <c r="C28" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A28)=1,WEEKDAY(A28)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A28,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A28,土日!$A$2:$A$28,0)),""))</f>
+        <v>235170</v>
+      </c>
+      <c r="F28" s="5" t="str">
+        <f aca="false">IF(E28="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A28,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A28,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <f aca="false">IF(AND(C28="平日",E28&lt;&gt;""),E28,"")</f>
+        <v>235170</v>
+      </c>
+      <c r="H28" s="7" t="str">
+        <f aca="false">IF(AND(C28="土日",E28&lt;&gt;""),E28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="38" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B29" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A29),1)</f>
+        <v>土</v>
+      </c>
+      <c r="C29" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A29)=1,WEEKDAY(A29)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D29" s="40"/>
+      <c r="E29" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A29,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A29,土日!$A$2:$A$28,0)),""))</f>
+        <v>569450</v>
+      </c>
+      <c r="F29" s="40" t="str">
+        <f aca="false">IF(E29="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A29,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A29,土日!$A$2:$A$28,0))))</f>
+        <v>棚橋　拓馬</v>
+      </c>
+      <c r="G29" s="41" t="str">
+        <f aca="false">IF(AND(C29="平日",E29&lt;&gt;""),E29,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="41" t="n">
+        <f aca="false">IF(AND(C29="土日",E29&lt;&gt;""),E29,"")</f>
+        <v>569450</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="38" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B30" s="39" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A30),1)</f>
+        <v>日</v>
+      </c>
+      <c r="C30" s="39" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A30)=1,WEEKDAY(A30)=7),"土日","平日")</f>
+        <v>土日</v>
+      </c>
+      <c r="D30" s="40"/>
+      <c r="E30" s="41" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A30,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A30,土日!$A$2:$A$28,0)),""))</f>
+        <v>512050</v>
+      </c>
+      <c r="F30" s="40" t="str">
+        <f aca="false">IF(E30="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A30,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A30,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G30" s="41" t="str">
+        <f aca="false">IF(AND(C30="平日",E30&lt;&gt;""),E30,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="41" t="n">
+        <f aca="false">IF(AND(C30="土日",E30&lt;&gt;""),E30,"")</f>
+        <v>512050</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B31" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A31),1)</f>
+        <v>月</v>
+      </c>
+      <c r="C31" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A31)=1,WEEKDAY(A31)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A31,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A31,土日!$A$2:$A$28,0)),""))</f>
+        <v>175910</v>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f aca="false">IF(E31="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A31,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A31,土日!$A$2:$A$28,0))))</f>
+        <v>もたい かずよし</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <f aca="false">IF(AND(C31="平日",E31&lt;&gt;""),E31,"")</f>
+        <v>175910</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <f aca="false">IF(AND(C31="土日",E31&lt;&gt;""),E31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B32" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A32),1)</f>
+        <v>火</v>
+      </c>
+      <c r="C32" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A32)=1,WEEKDAY(A32)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A32,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A32,土日!$A$2:$A$28,0)),""))</f>
+        <v>203590</v>
+      </c>
+      <c r="F32" s="5" t="str">
+        <f aca="false">IF(E32="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A32,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A32,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <f aca="false">IF(AND(C32="平日",E32&lt;&gt;""),E32,"")</f>
+        <v>203590</v>
+      </c>
+      <c r="H32" s="7" t="str">
+        <f aca="false">IF(AND(C32="土日",E32&lt;&gt;""),E32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B33" s="21" t="str">
+        <f aca="false">MID("日月火水木金土",WEEKDAY(A33),1)</f>
+        <v>水</v>
+      </c>
+      <c r="C33" s="21" t="str">
+        <f aca="false">IF(OR(WEEKDAY(A33)=1,WEEKDAY(A33)=7),"土日","平日")</f>
+        <v>平日</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="7" t="n">
+        <f aca="false">IFERROR(INDEX(平日!$C$2:$C$71,MATCH(A33,平日!$A$2:$A$71,0)),IFERROR(INDEX(土日!$C$2:$C$28,MATCH(A33,土日!$A$2:$A$28,0)),""))</f>
+        <v>204670</v>
+      </c>
+      <c r="F33" s="5" t="str">
+        <f aca="false">IF(E33="","報告なし",IFERROR(INDEX(平日!$D$2:$D$71,MATCH(A33,平日!$A$2:$A$71,0)),INDEX(土日!$D$2:$D$28,MATCH(A33,土日!$A$2:$A$28,0))))</f>
+        <v>大後戸あつし</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <f aca="false">IF(AND(C33="平日",E33&lt;&gt;""),E33,"")</f>
+        <v>204670</v>
+      </c>
+      <c r="H33" s="7" t="str">
+        <f aca="false">IF(AND(C33="土日",E33&lt;&gt;""),E33,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>